--- a/site/public/FoodSecurityProfile-definition.xlsx
+++ b/site/public/FoodSecurityProfile-definition.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>73 fields defined</t>
+          <t>83 fields defined</t>
         </is>
       </c>
     </row>
@@ -670,17 +670,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
@@ -752,62 +752,58 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>fcs_staples_days</t>
+          <t>identifiers</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>concept:Identifier</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Number of days in the past seven during which any member of the household consumed staple cereals, roots, and tubers. Part of the WFP Food Consumption Score (FCS).</t>
+          <t>Identifiers carried by this entity, such as national ID numbers, program IDs, or identifiers asserted by an identity document.</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé des céréales de base, des racines ou des tubercules. Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
+          <t>Identifiants portés par cette entité, tels que numéros d'identité nationale, identifiants de programme ou identifiants attestés par un document d'identité.</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>Número de días en los últimos siete en que algún miembro del hogar consumió cereales básicos, raíces y tubérculos. Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
+          <t>Identificadores que porta esta entidad, como números de identidad nacional, ID de programa o identificadores acreditados por un documento de identidad.</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr"/>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>normative</t>
         </is>
       </c>
       <c r="I2" s="8" t="n"/>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>food_security</t>
+          <t>identity</t>
         </is>
       </c>
       <c r="K2" s="8" t="n"/>
-      <c r="L2" s="8" t="inlineStr">
-        <is>
-          <t>wfp_fcs, wfp_cari</t>
-        </is>
-      </c>
+      <c r="L2" s="8" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>fcs_pulses_days</t>
+          <t>subject</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>concept:Party</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -817,17 +813,17 @@
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>Number of days in the past seven during which any member of the household consumed pulses, legumes, or nuts (including groundnuts, cashews, and other nuts). Part of the WFP Food Consumption Score (FCS).</t>
+          <t>The person or group that the profile or scoring event is about. Ranged at Party (not Agent) because Profiles observe receivers: persons and organised groups of persons (Household, Family, Farm). Institutional actors (Organizations) are described through their own Organization records, not as subjects of a Profile.</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé des légumineuses ou des noix (y compris arachides, noix de cajou et autres noix). Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
+          <t>La personne ou le groupe sur lequel porte le profil ou l'événement de notation. Typé sur Party (et non Agent) parce que les Profiles observent des bénéficiaires : personnes et groupes organisés de personnes (Household, Family, Farm). Les acteurs institutionnels (Organizations) sont décrits par leurs propres enregistrements Organization, non comme sujets d'un Profile.</t>
         </is>
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>Número de días en los últimos siete en que algún miembro del hogar consumió legumbres, leguminosas o frutos secos (incluidos cacahuetes, anacardos y otros frutos secos). Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
+          <t>La persona o grupo sobre el que trata el perfil o evento de puntuación. Tipado como Party (no Agent) porque los Profile observan receptores: personas y grupos organizados de personas (Household, Family, Farm). Los actores institucionales (Organizations) se describen mediante sus propios registros Organization, no como sujetos de un Profile.</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr"/>
@@ -837,27 +833,19 @@
         </is>
       </c>
       <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>food_security</t>
-        </is>
-      </c>
+      <c r="J3" s="10" t="n"/>
       <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="inlineStr">
-        <is>
-          <t>wfp_fcs, wfp_cari</t>
-        </is>
-      </c>
+      <c r="L3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>fcs_vegetables_days</t>
+          <t>observation_date</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -867,17 +855,17 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Number of days in the past seven during which any member of the household consumed vegetables and green leaves. Part of the WFP Food Consumption Score (FCS).</t>
+          <t>The date on which the profile data was collected (when the instrument was administered or the measurement taken).</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé des légumes et des feuilles vertes. Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
+          <t>La date à laquelle les données du profil ont été collectées (date d'administration de l'instrument ou de prise de mesure).</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Número de días en los últimos siete en que algún miembro del hogar consumió verduras y hojas verdes. Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
+          <t>La fecha en que se recopilaron los datos del perfil (fecha en que se administró el instrumento o se tomó la medición).</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr"/>
@@ -887,27 +875,19 @@
         </is>
       </c>
       <c r="I4" s="8" t="n"/>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>food_security</t>
-        </is>
-      </c>
+      <c r="J4" s="8" t="n"/>
       <c r="K4" s="8" t="n"/>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>wfp_fcs, wfp_cari</t>
-        </is>
-      </c>
+      <c r="L4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>fcs_fruit_days</t>
+          <t>performed_by</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>concept:Agent</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -917,17 +897,17 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Number of days in the past seven during which any member of the household consumed fruit. Part of the WFP Food Consumption Score (FCS).</t>
+          <t>The agent (enumerator, field officer, or agency) accountable for administering the instrument or taking the measurement. Typically a Person or an Organization. When a software tool captured or derived the data, record it separately as software_used; performed_by identifies who is responsible, not what ran the capture.</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé des fruits. Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
+          <t>L'agent (enquêteur, agent de terrain ou organisme) responsable de l'administration de l'instrument ou de la prise de mesure. Généralement une Person ou une Organization. Lorsqu'un outil logiciel a capturé ou dérivé les données, enregistrez-le séparément via software_used ; performed_by identifie qui est responsable, et non ce qui a réalisé la capture.</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>Número de días en los últimos siete en que algún miembro del hogar consumió frutas. Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
+          <t>El agente (encuestador, agente de campo u organismo) responsable de administrar el instrumento o tomar la medición. Normalmente una Person o una Organization. Cuando una herramienta de software capturó o derivó los datos, regístrelo por separado mediante software_used; performed_by identifica quién es responsable, no qué ejecutó la captura.</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr"/>
@@ -937,27 +917,19 @@
         </is>
       </c>
       <c r="I5" s="10" t="n"/>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>food_security</t>
-        </is>
-      </c>
+      <c r="J5" s="10" t="n"/>
       <c r="K5" s="10" t="n"/>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>wfp_fcs, wfp_cari</t>
-        </is>
-      </c>
+      <c r="L5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>fcs_meat_fish_eggs_days</t>
+          <t>instrument_used</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>concept:Instrument</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -967,17 +939,17 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Number of days in the past seven during which any member of the household consumed meat, fish, or eggs (beef, goat, poultry, pork, bushmeat, fresh or dried fish and seafood, eggs of any kind). Part of the WFP Food Consumption Score (FCS); the standard FCS questionnaire asks this as a single combined protein question.</t>
+          <t>Reference to the instrument (survey form, questionnaire, screening protocol, measurement procedure) administered in this profile record.</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé de la viande, du poisson ou des œufs (bœuf, chèvre, volaille, porc, viande de brousse, poisson et fruits de mer frais ou séchés, œufs de toute sorte). Fait partie du Score de consommation alimentaire (FCS) du PAM ; le questionnaire FCS standard pose cette question comme une seule question protéique combinée.</t>
+          <t>Référence à l'instrument (formulaire d'enquête, questionnaire, protocole de dépistage, procédure de mesure) administré dans cet enregistrement de profil.</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Número de días en los últimos siete en que algún miembro del hogar consumió carne, pescado o huevos (res, cabra, aves, cerdo, carne de monte, pescado y mariscos frescos o secos, huevos de cualquier tipo). Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA; el cuestionario FCS estándar formula esta pregunta como una única pregunta combinada de proteínas.</t>
+          <t>Referencia al instrumento (formulario de encuesta, cuestionario, protocolo de detección, procedimiento de medición) administrado en este registro de perfil.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr"/>
@@ -987,27 +959,19 @@
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>food_security</t>
-        </is>
-      </c>
+      <c r="J6" s="8" t="n"/>
       <c r="K6" s="8" t="n"/>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>wfp_fcs, wfp_cari</t>
-        </is>
-      </c>
+      <c r="L6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>fcs_dairy_days</t>
+          <t>software_used</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>concept:SoftwareAgent</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1017,17 +981,17 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Number of days in the past seven during which any member of the household consumed milk and dairy at meal-contributing quantities (NOT small amounts used as condiments). Part of the WFP Food Consumption Score (FCS).</t>
+          <t>The software that performed this step, recorded so the result can be reproduced or audited. Distinct from the accountable evaluator or performer (the person or organisation responsible), which is recorded separately.</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé du lait ou des produits laitiers en quantités contribuant au repas (et non en petites quantités utilisées comme condiment). Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
+          <t>Le logiciel qui a effectué cette étape, enregistré afin que le résultat puisse être reproduit ou audité. Distinct de l'évaluateur ou de l'exécutant responsable (la personne ou l'organisme qui en répond), enregistré séparément.</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Número de días en los últimos siete en que algún miembro del hogar consumió leche y lácteos en cantidades que contribuyen a la comida (NO pequeñas cantidades usadas como condimento). Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
+          <t>El software que ejecutó este paso, registrado para que el resultado pueda reproducirse o auditarse. Distinto del evaluador o ejecutor responsable (la persona u organismo que responde), que se registra por separado.</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
@@ -1037,27 +1001,19 @@
         </is>
       </c>
       <c r="I7" s="10" t="n"/>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>food_security</t>
-        </is>
-      </c>
+      <c r="J7" s="10" t="n"/>
       <c r="K7" s="10" t="n"/>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>wfp_fcs, wfp_cari</t>
-        </is>
-      </c>
+      <c r="L7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>fcs_fat_oil_days</t>
+          <t>administration_mode</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1067,47 +1023,43 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Number of days in the past seven during which any member of the household consumed cooking oil, butter, ghee, and other fats. Part of the WFP Food Consumption Score (FCS).</t>
+          <t>How the instrument was administered to the subject: self-report, proxy-report (someone else answering about the subject), assisted (the subject answering with help), or mixed. Washington Group analytical guidance recommends disaggregating prevalence by administration mode because proxy responses systematically underreport difficulty.</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé de l'huile de cuisson, du beurre, du ghee ou d'autres matières grasses. Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
+          <t>Comment l'instrument a été administré au sujet : auto-déclaration, déclaration par procuration (quelqu'un d'autre répondant au sujet du sujet), assisté (le sujet répondant avec aide) ou mixte. Les lignes directrices analytiques du Washington Group recommandent de désagréger la prévalence par mode d'administration, car les réponses par procuration sous-déclarent systématiquement la difficulté.</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Número de días en los últimos siete en que algún miembro del hogar consumió aceite de cocina, mantequilla, ghee u otras grasas. Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr"/>
+          <t>Cómo se administró el instrumento al sujeto: autoinforme, informe por terceros (otra persona responde sobre el sujeto), asistido (el sujeto responde con ayuda) o mixto. Las directrices analíticas del Washington Group recomiendan desagregar la prevalencia por modo de administración, ya que las respuestas por terceros subestiman sistemáticamente la dificultad.</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>administration-mode</t>
+        </is>
+      </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
       <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>food_security</t>
-        </is>
-      </c>
+      <c r="J8" s="8" t="n"/>
       <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>wfp_fcs, wfp_cari</t>
-        </is>
-      </c>
+      <c r="L8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>fcs_sugar_days</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>concept:Person</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -1117,17 +1069,17 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Number of days in the past seven during which any member of the household consumed sugar, honey, and sweet foods. Part of the WFP Food Consumption Score (FCS).</t>
+          <t>The person who provided the answers to the instrument, when different from the subject. Required whenever the administration mode is proxy or assisted.</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé du sucre, du miel ou des aliments sucrés. Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
+          <t>La personne qui a fourni les réponses à l'instrument, lorsqu'elle est différente du sujet. Requise lorsque le mode d'administration est par procuration ou assisté.</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Número de días en los últimos siete en que algún miembro del hogar consumió azúcar, miel y alimentos dulces. Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
+          <t>La persona que proporcionó las respuestas al instrumento, cuando es distinta del sujeto. Requerida cuando el modo de administración es por terceros o asistido.</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr"/>
@@ -1137,27 +1089,19 @@
         </is>
       </c>
       <c r="I9" s="10" t="n"/>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>food_security</t>
-        </is>
-      </c>
+      <c r="J9" s="10" t="n"/>
       <c r="K9" s="10" t="n"/>
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>wfp_fcs, wfp_cari</t>
-        </is>
-      </c>
+      <c r="L9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>fcs_condiments_days</t>
+          <t>respondent_relationship</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -1167,67 +1111,63 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Number of days in the past seven during which any member of the household consumed condiments, salt, spices, tea, or coffee used in small quantities. This is a screener item with FCS weight 0: frequent consumption of only condiments signals severe diet narrowing even though this group does not contribute to the composite score. Part of the WFP Food Consumption Score (FCS).</t>
+          <t>The relationship of the respondent to the subject (parent, spouse, guardian, caregiver, etc.). Uses relationship-type because it describes a person-to-person relationship, not a role within a group. Required whenever the administration mode is proxy or assisted.</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé des condiments, du sel, des épices, du thé ou du café en petites quantités. Il s'agit d'un item de dépistage de poids FCS 0 : la consommation fréquente de seuls condiments signale un rétrécissement sévère du régime alimentaire, même si ce groupe ne contribue pas au score composite. Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
+          <t>La relation du répondant avec le sujet (parent, conjoint, tuteur, aidant, etc.). Utilise relationship-type parce qu'elle décrit une relation entre deux personnes, et non un rôle au sein d'un groupe. Requise lorsque le mode d'administration est par procuration ou assisté.</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Número de días en los últimos siete en que algún miembro del hogar consumió condimentos, sal, especias, té o café en pequeñas cantidades. Es un ítem de detección con peso FCS 0: el consumo frecuente solo de condimentos señala un empobrecimiento severo de la dieta aunque este grupo no contribuya al puntaje compuesto. Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr"/>
+          <t>La relación del respondiente con el sujeto (padre o madre, cónyuge, tutor, cuidador, etc.). Usa relationship-type porque describe una relación entre personas, no un rol dentro de un grupo. Requerida cuando el modo de administración es por terceros o asistido.</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>relationship-type</t>
+        </is>
+      </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>food_security</t>
-        </is>
-      </c>
+      <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>wfp_fcs, wfp_cari</t>
-        </is>
-      </c>
+      <c r="L10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>rcsi_less_preferred_food_days</t>
+          <t>items_asked</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Number of days in the past seven during which the household relied on less preferred or less expensive food. Part of the WFP/CARE Reduced Coping Strategies Index (rCSI).</t>
+          <t>The PublicSchema property IDs that were actually asked during this administration. Lets adopters distinguish items that were asked and declined (answer absent) from items that were not asked at all. When omitted, the item set is assumed to be the default item_set of the instrument used. The intended producer is the form compiler or collection server, which populates this list from the form definition at submission time.</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Nombre de jours au cours des sept derniers jours pendant lesquels le ménage a eu recours à des aliments moins préférés ou moins chers. Fait partie de l'Indice réduit des stratégies d'adaptation (rCSI) du PAM/CARE.</t>
+          <t>Les identifiants de propriétés PublicSchema effectivement posées lors de cette administration. Permet aux adopteurs de distinguer les items posés et refusés (réponse absente) des items qui n'ont pas été posés du tout. En l'absence de cette liste, l'ensemble d'items est présumé correspondre à l'item_set par défaut de l'instrument utilisé. Le producteur prévu est le compilateur de formulaire ou le serveur de collecte, qui remplit cette liste à partir de la définition du formulaire au moment de la soumission.</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Número de días en los últimos siete en que el hogar recurrió a alimentos menos preferidos o menos costosos. Forma parte del Índice de Estrategias de Afrontamiento Reducido (rCSI) del PMA/CARE.</t>
+          <t>Los identificadores de propiedades PublicSchema realmente preguntados durante esta administración. Permite a los adoptantes distinguir ítems preguntados y rechazados (respuesta ausente) de ítems que no fueron preguntados. Cuando se omite, el conjunto de ítems se asume igual al item_set por defecto del instrumento utilizado. El productor previsto es el compilador de formularios o el servidor de recolección, que completa esta lista a partir de la definición del formulario al momento del envío.</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr"/>
@@ -1237,22 +1177,14 @@
         </is>
       </c>
       <c r="I11" s="10" t="n"/>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>food_security</t>
-        </is>
-      </c>
+      <c r="J11" s="10" t="n"/>
       <c r="K11" s="10" t="n"/>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>wfp_rcsi, wfp_cari</t>
-        </is>
-      </c>
+      <c r="L11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>rcsi_borrow_food_days</t>
+          <t>fcs_staples_days</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -1267,17 +1199,17 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Number of days in the past seven during which the household borrowed food or relied on help from friends or relatives. Part of the WFP/CARE Reduced Coping Strategies Index (rCSI).</t>
+          <t>Number of days in the past seven during which any member of the household consumed staple cereals, roots, and tubers. Part of the WFP Food Consumption Score (FCS).</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Nombre de jours au cours des sept derniers jours pendant lesquels le ménage a emprunté de la nourriture ou a compté sur l'aide d'amis ou de proches. Fait partie de l'Indice réduit des stratégies d'adaptation (rCSI) du PAM/CARE.</t>
+          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé des céréales de base, des racines ou des tubercules. Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Número de días en los últimos siete en que el hogar pidió alimentos prestados o dependió de la ayuda de amigos o familiares. Forma parte del Índice de Estrategias de Afrontamiento Reducido (rCSI) del PMA/CARE.</t>
+          <t>Número de días en los últimos siete en que algún miembro del hogar consumió cereales básicos, raíces y tubérculos. Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr"/>
@@ -1295,14 +1227,14 @@
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>wfp_rcsi, wfp_cari</t>
+          <t>wfp_fcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>rcsi_reduce_meal_size_days</t>
+          <t>fcs_pulses_days</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -1317,17 +1249,17 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Number of days in the past seven during which the household limited portion sizes at mealtimes. Part of the WFP/CARE Reduced Coping Strategies Index (rCSI).</t>
+          <t>Number of days in the past seven during which any member of the household consumed pulses, legumes, or nuts (including groundnuts, cashews, and other nuts). Part of the WFP Food Consumption Score (FCS).</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Nombre de jours au cours des sept derniers jours pendant lesquels le ménage a réduit la taille des portions lors des repas. Fait partie de l'Indice réduit des stratégies d'adaptation (rCSI) du PAM/CARE.</t>
+          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé des légumineuses ou des noix (y compris arachides, noix de cajou et autres noix). Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Número de días en los últimos siete en que el hogar redujo el tamaño de las porciones en las comidas. Forma parte del Índice de Estrategias de Afrontamiento Reducido (rCSI) del PMA/CARE.</t>
+          <t>Número de días en los últimos siete en que algún miembro del hogar consumió legumbres, leguminosas o frutos secos (incluidos cacahuetes, anacardos y otros frutos secos). Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr"/>
@@ -1345,14 +1277,14 @@
       <c r="K13" s="10" t="n"/>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>wfp_rcsi, wfp_cari</t>
+          <t>wfp_fcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>rcsi_reduce_meal_number_days</t>
+          <t>fcs_vegetables_days</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -1367,17 +1299,17 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Number of days in the past seven during which the household reduced the number of meals eaten per day. Part of the WFP/CARE Reduced Coping Strategies Index (rCSI).</t>
+          <t>Number of days in the past seven during which any member of the household consumed vegetables and green leaves. Part of the WFP Food Consumption Score (FCS).</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Nombre de jours au cours des sept derniers jours pendant lesquels le ménage a réduit le nombre de repas pris par jour. Fait partie de l'Indice réduit des stratégies d'adaptation (rCSI) du PAM/CARE.</t>
+          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé des légumes et des feuilles vertes. Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Número de días en los últimos siete en que el hogar redujo el número de comidas por día. Forma parte del Índice de Estrategias de Afrontamiento Reducido (rCSI) del PMA/CARE.</t>
+          <t>Número de días en los últimos siete en que algún miembro del hogar consumió verduras y hojas verdes. Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr"/>
@@ -1395,14 +1327,14 @@
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>wfp_rcsi, wfp_cari</t>
+          <t>wfp_fcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>rcsi_restrict_adult_consumption_days</t>
+          <t>fcs_fruit_days</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1417,17 +1349,17 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Number of days in the past seven during which the household restricted consumption by adults so that small children could eat. Part of the WFP/CARE Reduced Coping Strategies Index (rCSI).</t>
+          <t>Number of days in the past seven during which any member of the household consumed fruit. Part of the WFP Food Consumption Score (FCS).</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Nombre de jours au cours des sept derniers jours pendant lesquels le ménage a restreint la consommation des adultes pour que les jeunes enfants puissent manger. Fait partie de l'Indice réduit des stratégies d'adaptation (rCSI) du PAM/CARE.</t>
+          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé des fruits. Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Número de días en los últimos siete en que el hogar restringió el consumo de los adultos para que los niños pequeños pudieran comer. Forma parte del Índice de Estrategias de Afrontamiento Reducido (rCSI) del PMA/CARE.</t>
+          <t>Número de días en los últimos siete en que algún miembro del hogar consumió frutas. Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr"/>
@@ -1436,11 +1368,7 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
+      <c r="I15" s="10" t="n"/>
       <c r="J15" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -1449,19 +1377,19 @@
       <c r="K15" s="10" t="n"/>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>wfp_rcsi, wfp_cari</t>
+          <t>wfp_fcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>lcs_spent_savings</t>
+          <t>fcs_meat_fish_eggs_days</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1471,24 +1399,20 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Frequency with which the household spent savings to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, stress tier.</t>
+          <t>Number of days in the past seven during which any member of the household consumed meat, fish, or eggs (beef, goat, poultry, pork, bushmeat, fresh or dried fish and seafood, eggs of any kind). Part of the WFP Food Consumption Score (FCS); the standard FCS questionnaire asks this as a single combined protein question.</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle le ménage a dépensé ses économies pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de stress.</t>
+          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé de la viande, du poisson ou des œufs (bœuf, chèvre, volaille, porc, viande de brousse, poisson et fruits de mer frais ou séchés, œufs de toute sorte). Fait partie du Score de consommation alimentaire (FCS) du PAM ; le questionnaire FCS standard pose cette question comme une seule question protéique combinée.</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Frecuencia con la que el hogar gastó sus ahorros para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de estrés.</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>lcs-frequency</t>
-        </is>
-      </c>
+          <t>Número de días en los últimos siete en que algún miembro del hogar consumió carne, pescado o huevos (res, cabra, aves, cerdo, carne de monte, pescado y mariscos frescos o secos, huevos de cualquier tipo). Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA; el cuestionario FCS estándar formula esta pregunta como una única pregunta combinada de proteínas.</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr"/>
       <c r="H16" s="8" t="inlineStr">
         <is>
           <t>draft</t>
@@ -1503,19 +1427,19 @@
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>wfp_lcs, wfp_cari</t>
+          <t>wfp_fcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>lcs_sold_household_items</t>
+          <t>fcs_dairy_days</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1525,24 +1449,20 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Frequency with which the household sold household items (furniture, radio, jewellery) to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, stress tier.</t>
+          <t>Number of days in the past seven during which any member of the household consumed milk and dairy at meal-contributing quantities (NOT small amounts used as condiments). Part of the WFP Food Consumption Score (FCS).</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle le ménage a vendu des biens ménagers (meubles, radio, bijoux) pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de stress.</t>
+          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé du lait ou des produits laitiers en quantités contribuant au repas (et non en petites quantités utilisées comme condiment). Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Frecuencia con la que el hogar vendió artículos del hogar (muebles, radio, joyas) para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de estrés.</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>lcs-frequency</t>
-        </is>
-      </c>
+          <t>Número de días en los últimos siete en que algún miembro del hogar consumió leche y lácteos en cantidades que contribuyen a la comida (NO pequeñas cantidades usadas como condimento). Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr"/>
       <c r="H17" s="10" t="inlineStr">
         <is>
           <t>draft</t>
@@ -1557,19 +1477,19 @@
       <c r="K17" s="10" t="n"/>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>wfp_lcs, wfp_cari</t>
+          <t>wfp_fcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>lcs_reduced_nonfood_expenses</t>
+          <t>fcs_fat_oil_days</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1579,24 +1499,20 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Frequency with which the household reduced non-essential non-food spending, such as recreation or non-urgent purchases, to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, stress tier. Country adaptations vary on whether reductions in education spending sit here (stress) or in the crisis tier; operations should contextualise the tier assignment per country.</t>
+          <t>Number of days in the past seven during which any member of the household consumed cooking oil, butter, ghee, and other fats. Part of the WFP Food Consumption Score (FCS).</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle le ménage a réduit ses dépenses non alimentaires non essentielles, telles que les loisirs ou les achats non urgents, pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de stress. Les adaptations par pays varient sur le positionnement des réductions de dépenses d'éducation ici (stress) ou au niveau crise ; les opérations doivent contextualiser l'affectation par pays.</t>
+          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé de l'huile de cuisson, du beurre, du ghee ou d'autres matières grasses. Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Frecuencia con la que el hogar redujo gastos no alimentarios no esenciales, como recreación o compras no urgentes, para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de estrés. Las adaptaciones por país varían sobre si las reducciones del gasto en educación se ubican aquí (estrés) o en el nivel crisis; las operaciones deben contextualizar la asignación por país.</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>lcs-frequency</t>
-        </is>
-      </c>
+          <t>Número de días en los últimos siete en que algún miembro del hogar consumió aceite de cocina, mantequilla, ghee u otras grasas. Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr"/>
       <c r="H18" s="8" t="inlineStr">
         <is>
           <t>draft</t>
@@ -1611,19 +1527,19 @@
       <c r="K18" s="8" t="n"/>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>wfp_lcs, wfp_cari</t>
+          <t>wfp_fcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>lcs_borrowed_money_food</t>
+          <t>fcs_sugar_days</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -1633,24 +1549,20 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Frequency with which the household borrowed money or bought food on credit to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, stress tier.</t>
+          <t>Number of days in the past seven during which any member of the household consumed sugar, honey, and sweet foods. Part of the WFP Food Consumption Score (FCS).</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle le ménage a emprunté de l'argent ou acheté de la nourriture à crédit pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de stress.</t>
+          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé du sucre, du miel ou des aliments sucrés. Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Frecuencia con la que el hogar pidió dinero prestado o compró alimentos a crédito para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de estrés.</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>lcs-frequency</t>
-        </is>
-      </c>
+          <t>Número de días en los últimos siete en que algún miembro del hogar consumió azúcar, miel y alimentos dulces. Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr"/>
       <c r="H19" s="10" t="inlineStr">
         <is>
           <t>draft</t>
@@ -1665,19 +1577,19 @@
       <c r="K19" s="10" t="n"/>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>wfp_lcs, wfp_cari</t>
+          <t>wfp_fcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>lcs_sold_productive_assets</t>
+          <t>fcs_condiments_days</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -1687,24 +1599,20 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Frequency with which the household sold productive assets (tools, sewing machine, livestock) to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, crisis tier.</t>
+          <t>Number of days in the past seven during which any member of the household consumed condiments, salt, spices, tea, or coffee used in small quantities. This is a screener item with FCS weight 0: frequent consumption of only condiments signals severe diet narrowing even though this group does not contribute to the composite score. Part of the WFP Food Consumption Score (FCS).</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle le ménage a vendu des actifs productifs (outils, machine à coudre, bétail) pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de crise.</t>
+          <t>Nombre de jours au cours des sept derniers jours pendant lesquels au moins un membre du ménage a consommé des condiments, du sel, des épices, du thé ou du café en petites quantités. Il s'agit d'un item de dépistage de poids FCS 0 : la consommation fréquente de seuls condiments signale un rétrécissement sévère du régime alimentaire, même si ce groupe ne contribue pas au score composite. Fait partie du Score de consommation alimentaire (FCS) du PAM.</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Frecuencia con la que el hogar vendió activos productivos (herramientas, máquina de coser, ganado) para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de crisis.</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>lcs-frequency</t>
-        </is>
-      </c>
+          <t>Número de días en los últimos siete en que algún miembro del hogar consumió condimentos, sal, especias, té o café en pequeñas cantidades. Es un ítem de detección con peso FCS 0: el consumo frecuente solo de condimentos señala un empobrecimiento severo de la dieta aunque este grupo no contribuya al puntaje compuesto. Forma parte del Puntaje de Consumo de Alimentos (FCS) del PMA.</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr"/>
       <c r="H20" s="8" t="inlineStr">
         <is>
           <t>draft</t>
@@ -1719,19 +1627,19 @@
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>wfp_lcs, wfp_cari</t>
+          <t>wfp_fcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>lcs_withdrew_children_from_school</t>
+          <t>rcsi_less_preferred_food_days</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -1741,24 +1649,20 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Frequency with which the household withdrew children from school to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, crisis tier.</t>
+          <t>Number of days in the past seven during which the household relied on less preferred or less expensive food. Part of the WFP/CARE Reduced Coping Strategies Index (rCSI).</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle le ménage a retiré des enfants de l'école pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de crise.</t>
+          <t>Nombre de jours au cours des sept derniers jours pendant lesquels le ménage a eu recours à des aliments moins préférés ou moins chers. Fait partie de l'Indice réduit des stratégies d'adaptation (rCSI) du PAM/CARE.</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>Frecuencia con la que el hogar retiró niños de la escuela para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de crisis.</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>lcs-frequency</t>
-        </is>
-      </c>
+          <t>Número de días en los últimos siete en que el hogar recurrió a alimentos menos preferidos o menos costosos. Forma parte del Índice de Estrategias de Afrontamiento Reducido (rCSI) del PMA/CARE.</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr"/>
       <c r="H21" s="10" t="inlineStr">
         <is>
           <t>draft</t>
@@ -1773,19 +1677,19 @@
       <c r="K21" s="10" t="n"/>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>wfp_lcs, wfp_cari</t>
+          <t>wfp_rcsi, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>lcs_reduced_essential_nonfood</t>
+          <t>rcsi_borrow_food_days</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -1795,24 +1699,20 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Frequency with which the household reduced essential non-food spending, specifically health care, preventing access to needed treatment in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, crisis tier. Country adaptations vary on whether reductions in education spending sit here (crisis, when the reduction compromises schooling) or in the stress tier; operations should contextualise the tier assignment per country.</t>
+          <t>Number of days in the past seven during which the household borrowed food or relied on help from friends or relatives. Part of the WFP/CARE Reduced Coping Strategies Index (rCSI).</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle le ménage a réduit ses dépenses non alimentaires essentielles, plus précisément les soins de santé, empêchant l'accès aux traitements nécessaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de crise. Les adaptations par pays varient sur le positionnement des réductions de dépenses d'éducation ici (crise, lorsque la réduction compromet la scolarité) ou au niveau stress ; les opérations doivent contextualiser l'affectation par pays.</t>
+          <t>Nombre de jours au cours des sept derniers jours pendant lesquels le ménage a emprunté de la nourriture ou a compté sur l'aide d'amis ou de proches. Fait partie de l'Indice réduit des stratégies d'adaptation (rCSI) du PAM/CARE.</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Frecuencia con la que el hogar redujo gastos no alimentarios esenciales, específicamente la atención sanitaria, impidiendo el acceso al tratamiento necesario en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de crisis. Las adaptaciones por país varían sobre si las reducciones del gasto en educación se ubican aquí (crisis, cuando la reducción compromete la escolarización) o en el nivel estrés; las operaciones deben contextualizar la asignación por país.</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>lcs-frequency</t>
-        </is>
-      </c>
+          <t>Número de días en los últimos siete en que el hogar pidió alimentos prestados o dependió de la ayuda de amigos o familiares. Forma parte del Índice de Estrategias de Afrontamiento Reducido (rCSI) del PMA/CARE.</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr"/>
       <c r="H22" s="8" t="inlineStr">
         <is>
           <t>draft</t>
@@ -1827,19 +1727,19 @@
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>wfp_lcs, wfp_cari</t>
+          <t>wfp_rcsi, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>lcs_consumed_seed_stock</t>
+          <t>rcsi_reduce_meal_size_days</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -1849,24 +1749,20 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Frequency with which the household consumed seed stocks held for the next planting season to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, crisis tier.</t>
+          <t>Number of days in the past seven during which the household limited portion sizes at mealtimes. Part of the WFP/CARE Reduced Coping Strategies Index (rCSI).</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle le ménage a consommé des stocks de semences conservés pour la prochaine saison pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de crise.</t>
+          <t>Nombre de jours au cours des sept derniers jours pendant lesquels le ménage a réduit la taille des portions lors des repas. Fait partie de l'Indice réduit des stratégies d'adaptation (rCSI) du PAM/CARE.</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>Frecuencia con la que el hogar consumió reservas de semillas guardadas para la próxima siembra para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de crisis.</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>lcs-frequency</t>
-        </is>
-      </c>
+          <t>Número de días en los últimos siete en que el hogar redujo el tamaño de las porciones en las comidas. Forma parte del Índice de Estrategias de Afrontamiento Reducido (rCSI) del PMA/CARE.</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr"/>
       <c r="H23" s="10" t="inlineStr">
         <is>
           <t>draft</t>
@@ -1881,19 +1777,19 @@
       <c r="K23" s="10" t="n"/>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>wfp_lcs, wfp_cari</t>
+          <t>wfp_rcsi, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>lcs_harvested_immature_crops</t>
+          <t>rcsi_reduce_meal_number_days</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -1903,24 +1799,20 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Frequency with which the household harvested crops before maturity to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, crisis tier.</t>
+          <t>Number of days in the past seven during which the household reduced the number of meals eaten per day. Part of the WFP/CARE Reduced Coping Strategies Index (rCSI).</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle le ménage a récolté des cultures avant maturité pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de crise.</t>
+          <t>Nombre de jours au cours des sept derniers jours pendant lesquels le ménage a réduit le nombre de repas pris par jour. Fait partie de l'Indice réduit des stratégies d'adaptation (rCSI) du PAM/CARE.</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Frecuencia con la que el hogar cosechó cultivos antes de su madurez para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de crisis.</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>lcs-frequency</t>
-        </is>
-      </c>
+          <t>Número de días en los últimos siete en que el hogar redujo el número de comidas por día. Forma parte del Índice de Estrategias de Afrontamiento Reducido (rCSI) del PMA/CARE.</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr"/>
       <c r="H24" s="8" t="inlineStr">
         <is>
           <t>draft</t>
@@ -1935,19 +1827,19 @@
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>wfp_lcs, wfp_cari</t>
+          <t>wfp_rcsi, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>lcs_sold_house_or_land</t>
+          <t>rcsi_restrict_adult_consumption_days</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -1957,30 +1849,30 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Frequency with which the household sold the house or land to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, emergency tier.</t>
+          <t>Number of days in the past seven during which the household restricted consumption by adults so that small children could eat. Part of the WFP/CARE Reduced Coping Strategies Index (rCSI).</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle le ménage a vendu sa maison ou sa terre pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau d'urgence.</t>
+          <t>Nombre de jours au cours des sept derniers jours pendant lesquels le ménage a restreint la consommation des adultes pour que les jeunes enfants puissent manger. Fait partie de l'Indice réduit des stratégies d'adaptation (rCSI) du PAM/CARE.</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Frecuencia con la que el hogar vendió la vivienda o la tierra para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de emergencia.</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>lcs-frequency</t>
-        </is>
-      </c>
+          <t>Número de días en los últimos siete en que el hogar restringió el consumo de los adultos para que los niños pequeños pudieran comer. Forma parte del Índice de Estrategias de Afrontamiento Reducido (rCSI) del PMA/CARE.</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr"/>
       <c r="H25" s="10" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="I25" s="10" t="n"/>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -1989,14 +1881,14 @@
       <c r="K25" s="10" t="n"/>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>wfp_lcs, wfp_cari</t>
+          <t>wfp_rcsi, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>lcs_migrated_whole_household</t>
+          <t>lcs_spent_savings</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2011,17 +1903,17 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Frequency with which the whole household migrated to meet food needs in the past 30 days, distinct from seasonal or individual labour migration. Part of the WFP Livelihood Coping Strategies (LCS) module, emergency tier.</t>
+          <t>Frequency with which the household spent savings to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, stress tier.</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle l'ensemble du ménage a migré pour répondre à ses besoins alimentaires au cours des trente derniers jours, à distinguer de la migration saisonnière ou individuelle pour le travail. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau d'urgence.</t>
+          <t>Fréquence à laquelle le ménage a dépensé ses économies pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de stress.</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Frecuencia con la que todo el hogar migró para cubrir sus necesidades alimentarias en los últimos treinta días, distinto de la migración estacional o individual por trabajo. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de emergencia.</t>
+          <t>Frecuencia con la que el hogar gastó sus ahorros para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de estrés.</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
@@ -2050,7 +1942,7 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>lcs_child_labor</t>
+          <t>lcs_sold_household_items</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -2065,17 +1957,17 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Frequency with which household members, including children, engaged in exploitative or high-risk work to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, emergency tier. Protection red flag: affirmative responses warrant referral to the relevant child protection actors.</t>
+          <t>Frequency with which the household sold household items (furniture, radio, jewellery) to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, stress tier.</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle des membres du ménage, y compris des enfants, ont eu recours à un travail exploitant ou à haut risque pour répondre aux besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau d'urgence. Signal d'alerte en matière de protection : les réponses affirmatives justifient une orientation vers les acteurs de protection de l'enfance concernés.</t>
+          <t>Fréquence à laquelle le ménage a vendu des biens ménagers (meubles, radio, bijoux) pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de stress.</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>Frecuencia con la que miembros del hogar, incluidos niños, recurrieron a trabajo de explotación o de alto riesgo para cubrir las necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de emergencia. Señal de alerta de protección: las respuestas afirmativas justifican la derivación a los actores de protección infantil pertinentes.</t>
+          <t>Frecuencia con la que el hogar vendió artículos del hogar (muebles, radio, joyas) para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de estrés.</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -2088,11 +1980,7 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
+      <c r="I27" s="10" t="n"/>
       <c r="J27" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -2108,7 +1996,7 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>lcs_early_marriage</t>
+          <t>lcs_reduced_nonfood_expenses</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2123,17 +2011,17 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Frequency with which the household arranged the early marriage of a member (typically a girl) to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, emergency tier. Protection red flag: affirmative responses warrant referral to the relevant child protection and gender-based violence actors.</t>
+          <t>Frequency with which the household reduced non-essential non-food spending, such as recreation or non-urgent purchases, to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, stress tier. Country adaptations vary on whether reductions in education spending sit here (stress) or in the crisis tier; operations should contextualise the tier assignment per country.</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle le ménage a organisé le mariage précoce d'un membre (typiquement une fille) pour répondre aux besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau d'urgence. Signal d'alerte en matière de protection : les réponses affirmatives justifient une orientation vers les acteurs de protection de l'enfance et de lutte contre les violences basées sur le genre concernés.</t>
+          <t>Fréquence à laquelle le ménage a réduit ses dépenses non alimentaires non essentielles, telles que les loisirs ou les achats non urgents, pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de stress. Les adaptations par pays varient sur le positionnement des réductions de dépenses d'éducation ici (stress) ou au niveau crise ; les opérations doivent contextualiser l'affectation par pays.</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Frecuencia con la que el hogar concertó el matrimonio precoz de un miembro (típicamente una niña) para cubrir las necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de emergencia. Señal de alerta de protección: las respuestas afirmativas justifican la derivación a los actores de protección infantil y de violencia de género pertinentes.</t>
+          <t>Frecuencia con la que el hogar redujo gastos no alimentarios no esenciales, como recreación o compras no urgentes, para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de estrés. Las adaptaciones por país varían sobre si las reducciones del gasto en educación se ubican aquí (estrés) o en el nivel crisis; las operaciones deben contextualizar la asignación por país.</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -2146,11 +2034,7 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
+      <c r="I28" s="8" t="n"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -2166,7 +2050,7 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>lcs_begging</t>
+          <t>lcs_borrowed_money_food</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -2181,17 +2065,17 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Frequency with which the household begged for food or money to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, emergency tier.</t>
+          <t>Frequency with which the household borrowed money or bought food on credit to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, stress tier.</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle le ménage a mendié de la nourriture ou de l'argent pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau d'urgence.</t>
+          <t>Fréquence à laquelle le ménage a emprunté de l'argent ou acheté de la nourriture à crédit pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de stress.</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>Frecuencia con la que el hogar mendigó alimentos o dinero para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de emergencia.</t>
+          <t>Frecuencia con la que el hogar pidió dinero prestado o compró alimentos a crédito para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de estrés.</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
@@ -2204,11 +2088,7 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
+      <c r="I29" s="10" t="n"/>
       <c r="J29" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -2224,12 +2104,12 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>hdds_cereals_consumed</t>
+          <t>lcs_sold_productive_assets</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2239,20 +2119,24 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Whether any member of the household consumed an item from the cereals and grain products food group (bread, pasta, rice) in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
+          <t>Frequency with which the household sold productive assets (tools, sewing machine, livestock) to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, crisis tier.</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>Si un membre du ménage a consommé un aliment du groupe des céréales et produits céréaliers (pain, pâtes, riz) au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
+          <t>Fréquence à laquelle le ménage a vendu des actifs productifs (outils, machine à coudre, bétail) pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de crise.</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>Si algún miembro del hogar consumió un alimento del grupo de cereales y productos de granos (pan, pasta, arroz) en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr"/>
+          <t>Frecuencia con la que el hogar vendió activos productivos (herramientas, máquina de coser, ganado) para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de crisis.</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>lcs-frequency</t>
+        </is>
+      </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
           <t>draft</t>
@@ -2267,19 +2151,19 @@
       <c r="K30" s="8" t="n"/>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>fao_hdds</t>
+          <t>wfp_lcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>hdds_roots_tubers_consumed</t>
+          <t>lcs_withdrew_children_from_school</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -2289,20 +2173,24 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Whether any member of the household consumed an item from the white roots and tubers food group (white potato, white yam, cassava) in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
+          <t>Frequency with which the household withdrew children from school to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, crisis tier.</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Si un membre du ménage a consommé un aliment du groupe des racines et tubercules blancs (pomme de terre blanche, igname blanc, manioc) au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
+          <t>Fréquence à laquelle le ménage a retiré des enfants de l'école pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de crise.</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>Si algún miembro del hogar consumió un alimento del grupo de raíces y tubérculos blancos (papa blanca, ñame blanco, yuca) en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr"/>
+          <t>Frecuencia con la que el hogar retiró niños de la escuela para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de crisis.</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>lcs-frequency</t>
+        </is>
+      </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
           <t>draft</t>
@@ -2317,19 +2205,19 @@
       <c r="K31" s="10" t="n"/>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>fao_hdds</t>
+          <t>wfp_lcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>hdds_vegetables_consumed</t>
+          <t>lcs_reduced_essential_nonfood</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -2339,20 +2227,24 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Whether any member of the household consumed an item from the vegetables food group, including dark green leafy vegetables, in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
+          <t>Frequency with which the household reduced essential non-food spending, specifically health care, preventing access to needed treatment in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, crisis tier. Country adaptations vary on whether reductions in education spending sit here (crisis, when the reduction compromises schooling) or in the stress tier; operations should contextualise the tier assignment per country.</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Si un membre du ménage a consommé un aliment du groupe des légumes, y compris les légumes-feuilles vert foncé, au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
+          <t>Fréquence à laquelle le ménage a réduit ses dépenses non alimentaires essentielles, plus précisément les soins de santé, empêchant l'accès aux traitements nécessaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de crise. Les adaptations par pays varient sur le positionnement des réductions de dépenses d'éducation ici (crise, lorsque la réduction compromet la scolarité) ou au niveau stress ; les opérations doivent contextualiser l'affectation par pays.</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>Si algún miembro del hogar consumió un alimento del grupo de verduras, incluidas las hortalizas de hoja verde oscuro, en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr"/>
+          <t>Frecuencia con la que el hogar redujo gastos no alimentarios esenciales, específicamente la atención sanitaria, impidiendo el acceso al tratamiento necesario en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de crisis. Las adaptaciones por país varían sobre si las reducciones del gasto en educación se ubican aquí (crisis, cuando la reducción compromete la escolarización) o en el nivel estrés; las operaciones deben contextualizar la asignación por país.</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>lcs-frequency</t>
+        </is>
+      </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
           <t>draft</t>
@@ -2367,19 +2259,19 @@
       <c r="K32" s="8" t="n"/>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>fao_hdds</t>
+          <t>wfp_lcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>hdds_fruit_consumed</t>
+          <t>lcs_consumed_seed_stock</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -2389,20 +2281,24 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Whether any member of the household consumed an item from the fruits food group in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
+          <t>Frequency with which the household consumed seed stocks held for the next planting season to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, crisis tier.</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Si un membre du ménage a consommé un aliment du groupe des fruits au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
+          <t>Fréquence à laquelle le ménage a consommé des stocks de semences conservés pour la prochaine saison pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de crise.</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>Si algún miembro del hogar consumió un alimento del grupo de frutas en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr"/>
+          <t>Frecuencia con la que el hogar consumió reservas de semillas guardadas para la próxima siembra para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de crisis.</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>lcs-frequency</t>
+        </is>
+      </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
           <t>draft</t>
@@ -2417,19 +2313,19 @@
       <c r="K33" s="10" t="n"/>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>fao_hdds</t>
+          <t>wfp_lcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>hdds_meat_poultry_offal_consumed</t>
+          <t>lcs_harvested_immature_crops</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -2439,20 +2335,24 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Whether any member of the household consumed an item from the meat, poultry, and offal food group in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
+          <t>Frequency with which the household harvested crops before maturity to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, crisis tier.</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Si un membre du ménage a consommé un aliment du groupe de la viande, de la volaille et des abats au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
+          <t>Fréquence à laquelle le ménage a récolté des cultures avant maturité pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau de crise.</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>Si algún miembro del hogar consumió un alimento del grupo de carnes, aves y vísceras en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr"/>
+          <t>Frecuencia con la que el hogar cosechó cultivos antes de su madurez para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de crisis.</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>lcs-frequency</t>
+        </is>
+      </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
           <t>draft</t>
@@ -2467,19 +2367,19 @@
       <c r="K34" s="8" t="n"/>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>fao_hdds</t>
+          <t>wfp_lcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>hdds_eggs_consumed</t>
+          <t>lcs_sold_house_or_land</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -2489,20 +2389,24 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Whether any member of the household consumed an item from the eggs food group in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
+          <t>Frequency with which the household sold the house or land to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, emergency tier.</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Si un membre du ménage a consommé un aliment du groupe des œufs au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
+          <t>Fréquence à laquelle le ménage a vendu sa maison ou sa terre pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau d'urgence.</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>Si algún miembro del hogar consumió un alimento del grupo de los huevos en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr"/>
+          <t>Frecuencia con la que el hogar vendió la vivienda o la tierra para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de emergencia.</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>lcs-frequency</t>
+        </is>
+      </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
           <t>draft</t>
@@ -2517,19 +2421,19 @@
       <c r="K35" s="10" t="n"/>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>fao_hdds</t>
+          <t>wfp_lcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>hdds_fish_seafood_consumed</t>
+          <t>lcs_migrated_whole_household</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -2539,20 +2443,24 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Whether any member of the household consumed an item from the fish and seafood food group in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
+          <t>Frequency with which the whole household migrated to meet food needs in the past 30 days, distinct from seasonal or individual labour migration. Part of the WFP Livelihood Coping Strategies (LCS) module, emergency tier.</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Si un membre du ménage a consommé un aliment du groupe du poisson et des fruits de mer au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
+          <t>Fréquence à laquelle l'ensemble du ménage a migré pour répondre à ses besoins alimentaires au cours des trente derniers jours, à distinguer de la migration saisonnière ou individuelle pour le travail. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau d'urgence.</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Si algún miembro del hogar consumió un alimento del grupo de pescado y mariscos en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr"/>
+          <t>Frecuencia con la que todo el hogar migró para cubrir sus necesidades alimentarias en los últimos treinta días, distinto de la migración estacional o individual por trabajo. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de emergencia.</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>lcs-frequency</t>
+        </is>
+      </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
           <t>draft</t>
@@ -2567,19 +2475,19 @@
       <c r="K36" s="8" t="n"/>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>fao_hdds</t>
+          <t>wfp_lcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>hdds_legumes_nuts_seeds_consumed</t>
+          <t>lcs_child_labor</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -2589,26 +2497,34 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Whether any member of the household consumed an item from the legumes, nuts, and seeds food group (FAO group 8) in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
+          <t>Frequency with which household members, including children, engaged in exploitative or high-risk work to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, emergency tier. Protection red flag: affirmative responses warrant referral to the relevant child protection actors.</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Si un membre du ménage a consommé un aliment du groupe des légumineuses, noix et graines (groupe FAO 8) au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
+          <t>Fréquence à laquelle des membres du ménage, y compris des enfants, ont eu recours à un travail exploitant ou à haut risque pour répondre aux besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau d'urgence. Signal d'alerte en matière de protection : les réponses affirmatives justifient une orientation vers les acteurs de protection de l'enfance concernés.</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>Si algún miembro del hogar consumió un alimento del grupo de legumbres, nueces y semillas (grupo FAO 8) en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr"/>
+          <t>Frecuencia con la que miembros del hogar, incluidos niños, recurrieron a trabajo de explotación o de alto riesgo para cubrir las necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de emergencia. Señal de alerta de protección: las respuestas afirmativas justifican la derivación a los actores de protección infantil pertinentes.</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>lcs-frequency</t>
+        </is>
+      </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="I37" s="10" t="n"/>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -2617,19 +2533,19 @@
       <c r="K37" s="10" t="n"/>
       <c r="L37" s="10" t="inlineStr">
         <is>
-          <t>fao_hdds</t>
+          <t>wfp_lcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>hdds_milk_dairy_consumed</t>
+          <t>lcs_early_marriage</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -2639,26 +2555,34 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Whether any member of the household consumed an item from the milk and dairy products food group in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
+          <t>Frequency with which the household arranged the early marriage of a member (typically a girl) to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, emergency tier. Protection red flag: affirmative responses warrant referral to the relevant child protection and gender-based violence actors.</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Si un membre du ménage a consommé un aliment du groupe du lait et des produits laitiers au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
+          <t>Fréquence à laquelle le ménage a organisé le mariage précoce d'un membre (typiquement une fille) pour répondre aux besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau d'urgence. Signal d'alerte en matière de protection : les réponses affirmatives justifient une orientation vers les acteurs de protection de l'enfance et de lutte contre les violences basées sur le genre concernés.</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>Si algún miembro del hogar consumió un alimento del grupo de leche y productos lácteos en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr"/>
+          <t>Frecuencia con la que el hogar concertó el matrimonio precoz de un miembro (típicamente una niña) para cubrir las necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de emergencia. Señal de alerta de protección: las respuestas afirmativas justifican la derivación a los actores de protección infantil y de violencia de género pertinentes.</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>lcs-frequency</t>
+        </is>
+      </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="I38" s="8" t="n"/>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -2667,19 +2591,19 @@
       <c r="K38" s="8" t="n"/>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>fao_hdds</t>
+          <t>wfp_lcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>hdds_oils_fats_consumed</t>
+          <t>lcs_begging</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -2689,26 +2613,34 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Whether any member of the household consumed an item from the oils and fats food group in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
+          <t>Frequency with which the household begged for food or money to meet food needs in the past 30 days. Part of the WFP Livelihood Coping Strategies (LCS) module, emergency tier.</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Si un membre du ménage a consommé un aliment du groupe des huiles et matières grasses au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
+          <t>Fréquence à laquelle le ménage a mendié de la nourriture ou de l'argent pour répondre à ses besoins alimentaires au cours des trente derniers jours. Fait partie du module des stratégies de moyens d'existence (LCS) du PAM, niveau d'urgence.</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>Si algún miembro del hogar consumió un alimento del grupo de aceites y grasas en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
-        </is>
-      </c>
-      <c r="G39" s="10" t="inlineStr"/>
+          <t>Frecuencia con la que el hogar mendigó alimentos o dinero para cubrir sus necesidades alimentarias en los últimos treinta días. Forma parte del módulo de Estrategias de Medios de Vida (LCS) del PMA, nivel de emergencia.</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>lcs-frequency</t>
+        </is>
+      </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="I39" s="10" t="n"/>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -2717,14 +2649,14 @@
       <c r="K39" s="10" t="n"/>
       <c r="L39" s="10" t="inlineStr">
         <is>
-          <t>fao_hdds</t>
+          <t>wfp_lcs, wfp_cari</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>hdds_sweets_consumed</t>
+          <t>hdds_cereals_consumed</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -2739,17 +2671,17 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Whether any member of the household consumed an item from the sweets food group (sugar, honey, sweetened beverages, candies, cakes) in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
+          <t>Whether any member of the household consumed an item from the cereals and grain products food group (bread, pasta, rice) in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Si un membre du ménage a consommé un aliment du groupe des sucreries (sucre, miel, boissons sucrées, bonbons, gâteaux) au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
+          <t>Si un membre du ménage a consommé un aliment du groupe des céréales et produits céréaliers (pain, pâtes, riz) au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>Si algún miembro del hogar consumió un alimento del grupo de dulces (azúcar, miel, bebidas azucaradas, caramelos, pasteles) en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
+          <t>Si algún miembro del hogar consumió un alimento del grupo de cereales y productos de granos (pan, pasta, arroz) en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr"/>
@@ -2774,7 +2706,7 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>hdds_spices_condiments_beverages_consumed</t>
+          <t>hdds_roots_tubers_consumed</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -2789,17 +2721,17 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Whether any member of the household consumed an item from the spices, condiments, and beverages food group (FAO group 12) in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
+          <t>Whether any member of the household consumed an item from the white roots and tubers food group (white potato, white yam, cassava) in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Si un membre du ménage a consommé un aliment du groupe des épices, condiments et boissons (groupe FAO 12) au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
+          <t>Si un membre du ménage a consommé un aliment du groupe des racines et tubercules blancs (pomme de terre blanche, igname blanc, manioc) au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>Si algún miembro del hogar consumió un alimento del grupo de especias, condimentos y bebidas (grupo FAO 12) en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
+          <t>Si algún miembro del hogar consumió un alimento del grupo de raíces y tubérculos blancos (papa blanca, ñame blanco, yuca) en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr"/>
@@ -2824,7 +2756,7 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>fies_worried</t>
+          <t>hdds_vegetables_consumed</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -2839,17 +2771,17 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Whether, at any time during the FIES reference period, the household worried they would not have enough food because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
+          <t>Whether any member of the household consumed an item from the vegetables food group, including dark green leafy vegetables, in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>Si, à un moment quelconque de la période de référence FIES, le ménage a craint de ne pas avoir suffisamment de nourriture par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
+          <t>Si un membre du ménage a consommé un aliment du groupe des légumes, y compris les légumes-feuilles vert foncé, au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>Si en algún momento durante el período de referencia FIES, el hogar se preocupó de no tener suficiente comida por falta de recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
+          <t>Si algún miembro del hogar consumió un alimento del grupo de verduras, incluidas las hortalizas de hoja verde oscuro, en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr"/>
@@ -2858,11 +2790,7 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
+      <c r="I42" s="8" t="n"/>
       <c r="J42" s="8" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -2871,14 +2799,14 @@
       <c r="K42" s="8" t="n"/>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>fao_fies</t>
+          <t>fao_hdds</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>fies_unable_healthy_food</t>
+          <t>hdds_fruit_consumed</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
@@ -2893,17 +2821,17 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Whether, at any time during the FIES reference period, the household was unable to eat healthy and nutritious food because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
+          <t>Whether any member of the household consumed an item from the fruits food group in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Si, à un moment quelconque de la période de référence FIES, le ménage a été incapable de manger des aliments sains et nutritifs par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
+          <t>Si un membre du ménage a consommé un aliment du groupe des fruits au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>Si en algún momento durante el período de referencia FIES, el hogar no pudo comer alimentos saludables y nutritivos por falta de recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
+          <t>Si algún miembro del hogar consumió un alimento del grupo de frutas en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr"/>
@@ -2912,11 +2840,7 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
+      <c r="I43" s="10" t="n"/>
       <c r="J43" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -2925,14 +2849,14 @@
       <c r="K43" s="10" t="n"/>
       <c r="L43" s="10" t="inlineStr">
         <is>
-          <t>fao_fies</t>
+          <t>fao_hdds</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>fies_ate_few_foods</t>
+          <t>hdds_meat_poultry_offal_consumed</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -2947,17 +2871,17 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Whether, at any time during the FIES reference period, the household ate only a few kinds of foods because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
+          <t>Whether any member of the household consumed an item from the meat, poultry, and offal food group in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Si, à un moment quelconque de la période de référence FIES, le ménage n'a mangé que quelques types d'aliments par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
+          <t>Si un membre du ménage a consommé un aliment du groupe de la viande, de la volaille et des abats au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>Si en algún momento durante el período de referencia FIES, el hogar comió solo unos pocos tipos de alimentos por falta de recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
+          <t>Si algún miembro del hogar consumió un alimento del grupo de carnes, aves y vísceras en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr"/>
@@ -2966,11 +2890,7 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
+      <c r="I44" s="8" t="n"/>
       <c r="J44" s="8" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -2979,14 +2899,14 @@
       <c r="K44" s="8" t="n"/>
       <c r="L44" s="8" t="inlineStr">
         <is>
-          <t>fao_fies</t>
+          <t>fao_hdds</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>fies_skip_meal</t>
+          <t>hdds_eggs_consumed</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -3001,17 +2921,17 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Whether, at any time during the FIES reference period, the household had to skip a meal because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
+          <t>Whether any member of the household consumed an item from the eggs food group in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Si, à un moment quelconque de la période de référence FIES, le ménage a dû sauter un repas par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
+          <t>Si un membre du ménage a consommé un aliment du groupe des œufs au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>Si en algún momento durante el período de referencia FIES, el hogar tuvo que saltarse una comida por falta de recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
+          <t>Si algún miembro del hogar consumió un alimento del grupo de los huevos en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr"/>
@@ -3020,11 +2940,7 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
+      <c r="I45" s="10" t="n"/>
       <c r="J45" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -3033,14 +2949,14 @@
       <c r="K45" s="10" t="n"/>
       <c r="L45" s="10" t="inlineStr">
         <is>
-          <t>fao_fies</t>
+          <t>fao_hdds</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>fies_ate_less</t>
+          <t>hdds_fish_seafood_consumed</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -3055,17 +2971,17 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Whether, at any time during the FIES reference period, the household ate less than they thought they should because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
+          <t>Whether any member of the household consumed an item from the fish and seafood food group in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Si, à un moment quelconque de la période de référence FIES, le ménage a mangé moins qu'il ne pensait devoir manger par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
+          <t>Si un membre du ménage a consommé un aliment du groupe du poisson et des fruits de mer au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>Si en algún momento durante el período de referencia FIES, el hogar comió menos de lo que pensaba que debería porque le faltaban recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
+          <t>Si algún miembro del hogar consumió un alimento del grupo de pescado y mariscos en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr"/>
@@ -3074,11 +2990,7 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
+      <c r="I46" s="8" t="n"/>
       <c r="J46" s="8" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -3087,14 +2999,14 @@
       <c r="K46" s="8" t="n"/>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t>fao_fies</t>
+          <t>fao_hdds</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>fies_ran_out</t>
+          <t>hdds_legumes_nuts_seeds_consumed</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -3109,17 +3021,17 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Whether, at any time during the FIES reference period, the household ran out of food because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
+          <t>Whether any member of the household consumed an item from the legumes, nuts, and seeds food group (FAO group 8) in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Si, à un moment quelconque de la période de référence FIES, le ménage s'est retrouvé à court de nourriture par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
+          <t>Si un membre du ménage a consommé un aliment du groupe des légumineuses, noix et graines (groupe FAO 8) au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>Si en algún momento durante el período de referencia FIES, al hogar se le acabó la comida por falta de recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
+          <t>Si algún miembro del hogar consumió un alimento del grupo de legumbres, nueces y semillas (grupo FAO 8) en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr"/>
@@ -3128,11 +3040,7 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
+      <c r="I47" s="10" t="n"/>
       <c r="J47" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -3141,14 +3049,14 @@
       <c r="K47" s="10" t="n"/>
       <c r="L47" s="10" t="inlineStr">
         <is>
-          <t>fao_fies</t>
+          <t>fao_hdds</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>fies_hungry</t>
+          <t>hdds_milk_dairy_consumed</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -3163,17 +3071,17 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Whether, at any time during the FIES reference period, a member of the household was hungry but did not eat because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
+          <t>Whether any member of the household consumed an item from the milk and dairy products food group in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Si, à un moment quelconque de la période de référence FIES, un membre du ménage a eu faim mais n'a pas mangé par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
+          <t>Si un membre du ménage a consommé un aliment du groupe du lait et des produits laitiers au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>Si en algún momento durante el período de referencia FIES, algún miembro del hogar tuvo hambre pero no comió por falta de recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
+          <t>Si algún miembro del hogar consumió un alimento del grupo de leche y productos lácteos en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr"/>
@@ -3182,11 +3090,7 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
+      <c r="I48" s="8" t="n"/>
       <c r="J48" s="8" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -3195,14 +3099,14 @@
       <c r="K48" s="8" t="n"/>
       <c r="L48" s="8" t="inlineStr">
         <is>
-          <t>fao_fies</t>
+          <t>fao_hdds</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>fies_went_whole_day_without</t>
+          <t>hdds_oils_fats_consumed</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -3217,17 +3121,17 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Whether, at any time during the FIES reference period, a member of the household went without eating for a whole day because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
+          <t>Whether any member of the household consumed an item from the oils and fats food group in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Si, à un moment quelconque de la période de référence FIES, un membre du ménage est resté toute une journée sans manger par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
+          <t>Si un membre du ménage a consommé un aliment du groupe des huiles et matières grasses au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>Si en algún momento durante el período de referencia FIES, algún miembro del hogar pasó un día entero sin comer por falta de recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
+          <t>Si algún miembro del hogar consumió un alimento del grupo de aceites y grasas en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr"/>
@@ -3236,11 +3140,7 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
+      <c r="I49" s="10" t="n"/>
       <c r="J49" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -3249,19 +3149,19 @@
       <c r="K49" s="10" t="n"/>
       <c r="L49" s="10" t="inlineStr">
         <is>
-          <t>fao_fies</t>
+          <t>fao_hdds</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>hhs_no_food</t>
+          <t>hdds_sweets_consumed</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -3271,34 +3171,26 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Frequency with which, in the past 30 days, there was no food of any kind in the household because of lack of resources. One of three items in the FANTA Household Hunger Scale.</t>
+          <t>Whether any member of the household consumed an item from the sweets food group (sugar, honey, sweetened beverages, candies, cakes) in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle, au cours des 30 derniers jours, il n'y avait aucune nourriture d'aucune sorte dans le ménage par manque de ressources. L'un des trois items de l'Échelle de la faim du ménage (HHS) de FANTA.</t>
+          <t>Si un membre du ménage a consommé un aliment du groupe des sucreries (sucre, miel, boissons sucrées, bonbons, gâteaux) au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>Frecuencia con la que, en los últimos 30 días, no hubo ningún tipo de comida en el hogar por falta de recursos. Uno de los tres ítems de la Escala de Hambre del Hogar (HHS) de FANTA.</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>hhs-frequency</t>
-        </is>
-      </c>
+          <t>Si algún miembro del hogar consumió un alimento del grupo de dulces (azúcar, miel, bebidas azucaradas, caramelos, pasteles) en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr"/>
       <c r="H50" s="8" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
+      <c r="I50" s="8" t="n"/>
       <c r="J50" s="8" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -3307,19 +3199,19 @@
       <c r="K50" s="8" t="n"/>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>fanta_hhs</t>
+          <t>fao_hdds</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>hhs_went_sleep_hungry</t>
+          <t>hdds_spices_condiments_beverages_consumed</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -3329,34 +3221,26 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Frequency with which, in the past 30 days, any household member went to sleep at night hungry because there was not enough food. One of three items in the FANTA Household Hunger Scale.</t>
+          <t>Whether any member of the household consumed an item from the spices, condiments, and beverages food group (FAO group 12) in the past 24 hours. One of twelve food groups used by the FAO Household Dietary Diversity Score (HDDS).</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle, au cours des 30 derniers jours, un membre du ménage s'est couché le soir affamé parce qu'il n'y avait pas assez de nourriture. L'un des trois items de l'Échelle de la faim du ménage (HHS) de FANTA.</t>
+          <t>Si un membre du ménage a consommé un aliment du groupe des épices, condiments et boissons (groupe FAO 12) au cours des dernières 24 heures. L'un des douze groupes alimentaires utilisés par le Score de diversité alimentaire du ménage (HDDS) de la FAO.</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>Frecuencia con la que, en los últimos 30 días, algún miembro del hogar se fue a dormir por la noche con hambre porque no había suficiente comida. Uno de los tres ítems de la Escala de Hambre del Hogar (HHS) de FANTA.</t>
-        </is>
-      </c>
-      <c r="G51" s="10" t="inlineStr">
-        <is>
-          <t>hhs-frequency</t>
-        </is>
-      </c>
+          <t>Si algún miembro del hogar consumió un alimento del grupo de especias, condimentos y bebidas (grupo FAO 12) en las últimas 24 horas. Uno de los doce grupos alimentarios del Puntaje de Diversidad Dietética del Hogar (HDDS) de la FAO.</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t>sensitive</t>
-        </is>
-      </c>
+      <c r="I51" s="10" t="n"/>
       <c r="J51" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -3365,19 +3249,19 @@
       <c r="K51" s="10" t="n"/>
       <c r="L51" s="10" t="inlineStr">
         <is>
-          <t>fanta_hhs</t>
+          <t>fao_hdds</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>hhs_went_whole_day_without</t>
+          <t>fies_worried</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -3387,24 +3271,20 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Frequency with which, in the past 30 days, any household member went a whole day and night without eating because there was not enough food. One of three items in the FANTA Household Hunger Scale.</t>
+          <t>Whether, at any time during the FIES reference period, the household worried they would not have enough food because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Fréquence à laquelle, au cours des 30 derniers jours, un membre du ménage a passé une journée et une nuit entières sans manger parce qu'il n'y avait pas assez de nourriture. L'un des trois items de l'Échelle de la faim du ménage (HHS) de FANTA.</t>
+          <t>Si, à un moment quelconque de la période de référence FIES, le ménage a craint de ne pas avoir suffisamment de nourriture par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>Frecuencia con la que, en los últimos 30 días, algún miembro del hogar pasó un día y una noche enteros sin comer porque no había suficiente comida. Uno de los tres ítems de la Escala de Hambre del Hogar (HHS) de FANTA.</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>hhs-frequency</t>
-        </is>
-      </c>
+          <t>Si en algún momento durante el período de referencia FIES, el hogar se preocupó de no tener suficiente comida por falta de recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr"/>
       <c r="H52" s="8" t="inlineStr">
         <is>
           <t>draft</t>
@@ -3423,19 +3303,19 @@
       <c r="K52" s="8" t="n"/>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>fanta_hhs</t>
+          <t>fao_fies</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>mahfp_months_adequate</t>
+          <t>fies_unable_healthy_food</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -3445,17 +3325,17 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>The number of months, in the past 12, during which the household had enough food to meet its needs. Integer 0-12 (not schema-enforced). Output of the FANTA Months of Adequate Household Food Provisioning (MAHFP) indicator.</t>
+          <t>Whether, at any time during the FIES reference period, the household was unable to eat healthy and nutritious food because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Le nombre de mois, parmi les 12 derniers, pendant lesquels le ménage a eu suffisamment de nourriture pour couvrir ses besoins. Entier de 0 à 12 (non imposé par le schéma). Résultat de l'indicateur MAHFP de FANTA (Mois d'approvisionnement alimentaire adéquat du ménage).</t>
+          <t>Si, à un moment quelconque de la période de référence FIES, le ménage a été incapable de manger des aliments sains et nutritifs par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>El número de meses, en los últimos 12, durante los cuales el hogar tuvo suficiente comida para satisfacer sus necesidades. Entero 0-12 (no impuesto por el esquema). Resultado del indicador MAHFP de FANTA (Meses de Aprovisionamiento Alimentario Adecuado del Hogar).</t>
+          <t>Si en algún momento durante el período de referencia FIES, el hogar no pudo comer alimentos saludables y nutritivos por falta de recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr"/>
@@ -3464,7 +3344,11 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I53" s="10" t="n"/>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
@@ -3473,14 +3357,14 @@
       <c r="K53" s="10" t="n"/>
       <c r="L53" s="10" t="inlineStr">
         <is>
-          <t>fao_mahfp</t>
+          <t>fao_fies</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>wdds_grains_consumed</t>
+          <t>fies_ate_few_foods</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
@@ -3495,17 +3379,17 @@
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Whether the woman consumed an item from the grains, white roots and tubers, and plantains food group in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
+          <t>Whether, at any time during the FIES reference period, the household ate only a few kinds of foods because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Si la femme a consommé un aliment du groupe des céréales, racines et tubercules blancs et plantains au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
+          <t>Si, à un moment quelconque de la période de référence FIES, le ménage n'a mangé que quelques types d'aliments par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>Si la mujer consumió un alimento del grupo de cereales, raíces y tubérculos blancos y plátanos en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
+          <t>Si en algún momento durante el período de referencia FIES, el hogar comió solo unos pocos tipos de alimentos por falta de recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr"/>
@@ -3514,27 +3398,27 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I54" s="8" t="n"/>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
           <t>food_security</t>
         </is>
       </c>
-      <c r="K54" s="8" t="inlineStr">
-        <is>
-          <t>adolescent, adult</t>
-        </is>
-      </c>
+      <c r="K54" s="8" t="n"/>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>fao_wdds</t>
+          <t>fao_fies</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>wdds_pulses_consumed</t>
+          <t>fies_skip_meal</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -3549,17 +3433,17 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Whether the woman consumed an item from the pulses food group in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
+          <t>Whether, at any time during the FIES reference period, the household had to skip a meal because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Si la femme a consommé un aliment du groupe des légumineuses au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
+          <t>Si, à un moment quelconque de la période de référence FIES, le ménage a dû sauter un repas par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>Si la mujer consumió un alimento del grupo de las legumbres en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
+          <t>Si en algún momento durante el período de referencia FIES, el hogar tuvo que saltarse una comida por falta de recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr"/>
@@ -3568,27 +3452,27 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I55" s="10" t="n"/>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
         </is>
       </c>
-      <c r="K55" s="10" t="inlineStr">
-        <is>
-          <t>adolescent, adult</t>
-        </is>
-      </c>
+      <c r="K55" s="10" t="n"/>
       <c r="L55" s="10" t="inlineStr">
         <is>
-          <t>fao_wdds</t>
+          <t>fao_fies</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>wdds_nuts_seeds_consumed</t>
+          <t>fies_ate_less</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
@@ -3603,17 +3487,17 @@
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Whether the woman consumed an item from the nuts and seeds food group in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
+          <t>Whether, at any time during the FIES reference period, the household ate less than they thought they should because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Si la femme a consommé un aliment du groupe des noix et graines au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
+          <t>Si, à un moment quelconque de la période de référence FIES, le ménage a mangé moins qu'il ne pensait devoir manger par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>Si la mujer consumió un alimento del grupo de nueces y semillas en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
+          <t>Si en algún momento durante el período de referencia FIES, el hogar comió menos de lo que pensaba que debería porque le faltaban recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr"/>
@@ -3622,27 +3506,27 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I56" s="8" t="n"/>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
           <t>food_security</t>
         </is>
       </c>
-      <c r="K56" s="8" t="inlineStr">
-        <is>
-          <t>adolescent, adult</t>
-        </is>
-      </c>
+      <c r="K56" s="8" t="n"/>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>fao_wdds</t>
+          <t>fao_fies</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>wdds_dairy_consumed</t>
+          <t>fies_ran_out</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -3657,17 +3541,17 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Whether the woman consumed dairy products at meal-contributing quantities in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
+          <t>Whether, at any time during the FIES reference period, the household ran out of food because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Si la femme a consommé des produits laitiers en quantités contribuant à un repas au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
+          <t>Si, à un moment quelconque de la période de référence FIES, le ménage s'est retrouvé à court de nourriture par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>Si la mujer consumió productos lácteos en cantidades que contribuyen a una comida en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
+          <t>Si en algún momento durante el período de referencia FIES, al hogar se le acabó la comida por falta de recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr"/>
@@ -3676,27 +3560,27 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I57" s="10" t="n"/>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
         </is>
       </c>
-      <c r="K57" s="10" t="inlineStr">
-        <is>
-          <t>adolescent, adult</t>
-        </is>
-      </c>
+      <c r="K57" s="10" t="n"/>
       <c r="L57" s="10" t="inlineStr">
         <is>
-          <t>fao_wdds</t>
+          <t>fao_fies</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>wdds_meat_poultry_fish_consumed</t>
+          <t>fies_hungry</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
@@ -3711,17 +3595,17 @@
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Whether the woman consumed an item from the meat, poultry, and fish food group in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
+          <t>Whether, at any time during the FIES reference period, a member of the household was hungry but did not eat because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Si la femme a consommé un aliment du groupe de la viande, de la volaille et du poisson au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
+          <t>Si, à un moment quelconque de la période de référence FIES, un membre du ménage a eu faim mais n'a pas mangé par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>Si la mujer consumió un alimento del grupo de carne, aves y pescado en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
+          <t>Si en algún momento durante el período de referencia FIES, algún miembro del hogar tuvo hambre pero no comió por falta de recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr"/>
@@ -3730,27 +3614,27 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I58" s="8" t="n"/>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
           <t>food_security</t>
         </is>
       </c>
-      <c r="K58" s="8" t="inlineStr">
-        <is>
-          <t>adolescent, adult</t>
-        </is>
-      </c>
+      <c r="K58" s="8" t="n"/>
       <c r="L58" s="8" t="inlineStr">
         <is>
-          <t>fao_wdds</t>
+          <t>fao_fies</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>wdds_eggs_consumed</t>
+          <t>fies_went_whole_day_without</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -3765,17 +3649,17 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Whether the woman consumed eggs in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
+          <t>Whether, at any time during the FIES reference period, a member of the household went without eating for a whole day because of lack of resources. One of eight experience-based items in the FAO Food Insecurity Experience Scale (FIES); the reference period is recorded in recall_period_days.</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Si la femme a consommé des œufs au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
+          <t>Si, à un moment quelconque de la période de référence FIES, un membre du ménage est resté toute une journée sans manger par manque de ressources. L'un des huit items expérientiels de l'Échelle d'expérience de l'insécurité alimentaire (FIES) de la FAO ; la période de référence est enregistrée dans recall_period_days.</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>Si la mujer consumió huevos en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
+          <t>Si en algún momento durante el período de referencia FIES, algún miembro del hogar pasó un día entero sin comer por falta de recursos. Uno de los ocho ítems basados en experiencia de la Escala de Experiencia de Inseguridad Alimentaria (FIES) de la FAO; el período de referencia se registra en recall_period_days.</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr"/>
@@ -3784,32 +3668,32 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="I59" s="10" t="n"/>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
         </is>
       </c>
-      <c r="K59" s="10" t="inlineStr">
-        <is>
-          <t>adolescent, adult</t>
-        </is>
-      </c>
+      <c r="K59" s="10" t="n"/>
       <c r="L59" s="10" t="inlineStr">
         <is>
-          <t>fao_wdds</t>
+          <t>fao_fies</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>wdds_dark_green_leafy_veg_consumed</t>
+          <t>hhs_no_food</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -3819,51 +3703,55 @@
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Whether the woman consumed dark green leafy vegetables in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
+          <t>Frequency with which, in the past 30 days, there was no food of any kind in the household because of lack of resources. One of three items in the FANTA Household Hunger Scale.</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>Si la femme a consommé des légumes-feuilles vert foncé au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
+          <t>Fréquence à laquelle, au cours des 30 derniers jours, il n'y avait aucune nourriture d'aucune sorte dans le ménage par manque de ressources. L'un des trois items de l'Échelle de la faim du ménage (HHS) de FANTA.</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>Si la mujer consumió hortalizas de hoja verde oscuro en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
-        </is>
-      </c>
-      <c r="G60" s="8" t="inlineStr"/>
+          <t>Frecuencia con la que, en los últimos 30 días, no hubo ningún tipo de comida en el hogar por falta de recursos. Uno de los tres ítems de la Escala de Hambre del Hogar (HHS) de FANTA.</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>hhs-frequency</t>
+        </is>
+      </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="I60" s="8" t="n"/>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
           <t>food_security</t>
         </is>
       </c>
-      <c r="K60" s="8" t="inlineStr">
-        <is>
-          <t>adolescent, adult</t>
-        </is>
-      </c>
+      <c r="K60" s="8" t="n"/>
       <c r="L60" s="8" t="inlineStr">
         <is>
-          <t>fao_wdds</t>
+          <t>fanta_hhs</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>wdds_vitamin_a_fruit_veg_consumed</t>
+          <t>hhs_went_sleep_hungry</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -3873,51 +3761,55 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Whether the woman consumed other vitamin-A-rich fruits and vegetables (orange-fleshed sweet potato, mango, papaya, carrot, pumpkin) in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
+          <t>Frequency with which, in the past 30 days, any household member went to sleep at night hungry because there was not enough food. One of three items in the FANTA Household Hunger Scale.</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Si la femme a consommé d'autres fruits et légumes riches en vitamine A (patate douce à chair orange, mangue, papaye, carotte, citrouille) au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
+          <t>Fréquence à laquelle, au cours des 30 derniers jours, un membre du ménage s'est couché le soir affamé parce qu'il n'y avait pas assez de nourriture. L'un des trois items de l'Échelle de la faim du ménage (HHS) de FANTA.</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>Si la mujer consumió otras frutas y verduras ricas en vitamina A (batata de pulpa naranja, mango, papaya, zanahoria, calabaza) en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
-        </is>
-      </c>
-      <c r="G61" s="10" t="inlineStr"/>
+          <t>Frecuencia con la que, en los últimos 30 días, algún miembro del hogar se fue a dormir por la noche con hambre porque no había suficiente comida. Uno de los tres ítems de la Escala de Hambre del Hogar (HHS) de FANTA.</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>hhs-frequency</t>
+        </is>
+      </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="I61" s="10" t="n"/>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
           <t>food_security</t>
         </is>
       </c>
-      <c r="K61" s="10" t="inlineStr">
-        <is>
-          <t>adolescent, adult</t>
-        </is>
-      </c>
+      <c r="K61" s="10" t="n"/>
       <c r="L61" s="10" t="inlineStr">
         <is>
-          <t>fao_wdds</t>
+          <t>fanta_hhs</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>wdds_other_vegetables_consumed</t>
+          <t>hhs_went_whole_day_without</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -3927,51 +3819,55 @@
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Whether the woman consumed other vegetables (not dark green leafy or vitamin-A-rich) in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
+          <t>Frequency with which, in the past 30 days, any household member went a whole day and night without eating because there was not enough food. One of three items in the FANTA Household Hunger Scale.</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>Si la femme a consommé d'autres légumes (ni légumes-feuilles vert foncé ni riches en vitamine A) au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
+          <t>Fréquence à laquelle, au cours des 30 derniers jours, un membre du ménage a passé une journée et une nuit entières sans manger parce qu'il n'y avait pas assez de nourriture. L'un des trois items de l'Échelle de la faim du ménage (HHS) de FANTA.</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>Si la mujer consumió otras verduras (que no sean de hoja verde oscuro ni ricas en vitamina A) en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
-        </is>
-      </c>
-      <c r="G62" s="8" t="inlineStr"/>
+          <t>Frecuencia con la que, en los últimos 30 días, algún miembro del hogar pasó un día y una noche enteros sin comer porque no había suficiente comida. Uno de los tres ítems de la Escala de Hambre del Hogar (HHS) de FANTA.</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>hhs-frequency</t>
+        </is>
+      </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
-      <c r="I62" s="8" t="n"/>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>sensitive</t>
+        </is>
+      </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
           <t>food_security</t>
         </is>
       </c>
-      <c r="K62" s="8" t="inlineStr">
-        <is>
-          <t>adolescent, adult</t>
-        </is>
-      </c>
+      <c r="K62" s="8" t="n"/>
       <c r="L62" s="8" t="inlineStr">
         <is>
-          <t>fao_wdds</t>
+          <t>fanta_hhs</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>wdds_other_fruits_consumed</t>
+          <t>mahfp_months_adequate</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -3981,17 +3877,17 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Whether the woman consumed other fruits (not vitamin-A-rich) in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
+          <t>The number of months, in the past 12, during which the household had enough food to meet its needs. Integer 0-12 (not schema-enforced). Output of the FANTA Months of Adequate Household Food Provisioning (MAHFP) indicator.</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Si la femme a consommé d'autres fruits (non riches en vitamine A) au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
+          <t>Le nombre de mois, parmi les 12 derniers, pendant lesquels le ménage a eu suffisamment de nourriture pour couvrir ses besoins. Entier de 0 à 12 (non imposé par le schéma). Résultat de l'indicateur MAHFP de FANTA (Mois d'approvisionnement alimentaire adéquat du ménage).</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>Si la mujer consumió otras frutas (que no sean ricas en vitamina A) en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
+          <t>El número de meses, en los últimos 12, durante los cuales el hogar tuvo suficiente comida para satisfacer sus necesidades. Entero 0-12 (no impuesto por el esquema). Resultado del indicador MAHFP de FANTA (Meses de Aprovisionamiento Alimentario Adecuado del Hogar).</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr"/>
@@ -4006,26 +3902,22 @@
           <t>food_security</t>
         </is>
       </c>
-      <c r="K63" s="10" t="inlineStr">
-        <is>
-          <t>adolescent, adult</t>
-        </is>
-      </c>
+      <c r="K63" s="10" t="n"/>
       <c r="L63" s="10" t="inlineStr">
         <is>
-          <t>fao_wdds</t>
+          <t>fao_mahfp</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>recall_period_days</t>
+          <t>wdds_grains_consumed</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -4035,17 +3927,17 @@
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Number of days of recall for instrument items that allow a variable reference period, primarily FIES (commonly 30 or 365 days) and HDDS/WDDS variants. May be omitted when the reference period is fixed by the instrument protocol, but populating it explicitly is valid and can aid data quality verification. Canonical recall periods by instrument: FCS 7 days, rCSI 7 days, HDDS 1 day, MDD-W 1 day, FIES 30 days (operational monitoring) or 365 days (SDG 2.1.2), HHS 30 days, LCS 30 days, MAHFP 12 months. Multi-instrument profiles pick one value, typically the longest.</t>
+          <t>Whether the woman consumed an item from the grains, white roots and tubers, and plantains food group in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>Nombre de jours de rappel pour les items d'instruments permettant une période de référence variable, principalement FIES (couramment 30 ou 365 jours) et les variantes HDDS/MDD-W. Peut être omis lorsque la période de référence est fixée par le protocole de l'instrument, mais le renseigner explicitement est valide et peut faciliter la vérification de la qualité des données. Périodes de rappel canoniques par instrument : FCS 7 jours, rCSI 7 jours, HDDS 1 jour, MDD-W 1 jour, FIES 30 jours (suivi opérationnel) ou 365 jours (ODD 2.1.2), HHS 30 jours, LCS 30 jours, MAHFP 12 mois. Les profils multi-instruments choisissent une valeur, généralement la plus longue.</t>
+          <t>Si la femme a consommé un aliment du groupe des céréales, racines et tubercules blancs et plantains au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>Número de días de recordatorio para los ítems de instrumentos que permiten un período de referencia variable, principalmente FIES (comúnmente 30 o 365 días) y variantes HDDS/MDD-W. Puede omitirse cuando el período de referencia está fijado por el protocolo del instrumento, pero registrarlo explícitamente es válido y puede facilitar la verificación de calidad de datos. Períodos de recordatorio canónicos por instrumento: FCS 7 días, rCSI 7 días, HDDS 1 día, MDD-W 1 día, FIES 30 días (monitoreo operativo) o 365 días (ODS 2.1.2), HHS 30 días, LCS 30 días, MAHFP 12 meses. Los perfiles multi-instrumento eligen un valor, generalmente el más largo.</t>
+          <t>Si la mujer consumió un alimento del grupo de cereales, raíces y tubérculos blancos y plátanos en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr"/>
@@ -4057,21 +3949,29 @@
       <c r="I64" s="8" t="n"/>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>context</t>
-        </is>
-      </c>
-      <c r="K64" s="8" t="n"/>
-      <c r="L64" s="8" t="n"/>
+          <t>food_security</t>
+        </is>
+      </c>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>adolescent, adult</t>
+        </is>
+      </c>
+      <c r="L64" s="8" t="inlineStr">
+        <is>
+          <t>fao_wdds</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>fcs_score</t>
+          <t>wdds_pulses_consumed</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -4081,17 +3981,17 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>The weighted Food Consumption Score for this administration, calculated as the sum of food-group frequency days multiplied by their WFP standard weights. Range 0-112. The canonical scoring uses nine food groups with weights from the WFP FCS Technical Guidance Note (2015).</t>
+          <t>Whether the woman consumed an item from the pulses food group in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Le score de consommation alimentaire (FCS) pondéré pour cette passation, calculé comme la somme des jours de fréquence par groupe alimentaire multipliés par leurs poids standard du PAM. Plage 0-112. La notation canonique utilise neuf groupes alimentaires avec les poids du Guide technique FCS du PAM (2015).</t>
+          <t>Si la femme a consommé un aliment du groupe des légumineuses au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>El puntaje ponderado de consumo alimentario (FCS) para esta aplicación, calculado como la suma de los días de frecuencia por grupo alimentario multiplicados por sus pesos estándar del PMA. Rango 0-112. La puntuación canónica usa nueve grupos alimentarios con los pesos de la Guía Técnica FCS del PMA (2015).</t>
+          <t>Si la mujer consumió un alimento del grupo de las legumbres en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr"/>
@@ -4106,22 +4006,26 @@
           <t>food_security</t>
         </is>
       </c>
-      <c r="K65" s="10" t="n"/>
+      <c r="K65" s="10" t="inlineStr">
+        <is>
+          <t>adolescent, adult</t>
+        </is>
+      </c>
       <c r="L65" s="10" t="inlineStr">
         <is>
-          <t>wfp_fcs</t>
+          <t>fao_wdds</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>fcs_consumption_group</t>
+          <t>wdds_nuts_seeds_consumed</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -4131,24 +4035,20 @@
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>The food consumption group derived from fcs_score using WFP-published thresholds. Both the standard set (21/35) and the high-sugar/high-oil set (28/42) are WFP-canonical and valid for this field. Use ScoringEvent only for thresholds not published by WFP (national adaptations, researcher-defined cutoffs). Standard thresholds: poor (0-21), borderline (21.5-35), acceptable (&gt; 35). Adjusted thresholds for high-sugar/high-oil contexts: poor (0-28), borderline (28.5-42), acceptable (&gt; 42).</t>
+          <t>Whether the woman consumed an item from the nuts and seeds food group in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>Le groupe de consommation alimentaire dérivé du fcs_score selon les seuils publiés par le PAM. Les seuils standard (21/35) et les seuils ajustés pour les régimes riches en sucre ou en huile (28/42) sont tous deux canoniques et valides pour ce champ. Utiliser ScoringEvent uniquement pour des seuils non publiés par le PAM (adaptations nationales, seuils définis par des chercheurs). Seuils standard : pauvre (0-21), limite (21,5-35), acceptable (&gt; 35). Seuils ajustés : pauvre (0-28), limite (28,5-42), acceptable (&gt; 42).</t>
+          <t>Si la femme a consommé un aliment du groupe des noix et graines au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>El grupo de consumo alimentario derivado del fcs_score según los umbrales publicados por el PMA. Tanto el conjunto estándar (21/35) como el conjunto ajustado para dietas altas en azúcar o aceite (28/42) son canónicos del PMA y válidos para este campo. Usar ScoringEvent solo para umbrales no publicados por el PMA (adaptaciones nacionales, cortes definidos por investigadores). Umbrales estándar: pobre (0-21), límite (21,5-35), aceptable (&gt; 35). Umbrales ajustados: pobre (0-28), límite (28,5-42), aceptable (&gt; 42).</t>
-        </is>
-      </c>
-      <c r="G66" s="8" t="inlineStr">
-        <is>
-          <t>food-consumption-group</t>
-        </is>
-      </c>
+          <t>Si la mujer consumió un alimento del grupo de nueces y semillas en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr"/>
       <c r="H66" s="8" t="inlineStr">
         <is>
           <t>draft</t>
@@ -4160,22 +4060,26 @@
           <t>food_security</t>
         </is>
       </c>
-      <c r="K66" s="8" t="n"/>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>adolescent, adult</t>
+        </is>
+      </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
-          <t>wfp_fcs</t>
+          <t>fao_wdds</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>rcsi_score</t>
+          <t>wdds_dairy_consumed</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -4185,17 +4089,17 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>The reduced Coping Strategies Index score for this administration, calculated as the weighted sum of five coping strategy frequency days. Range 0-56. Higher scores indicate greater food insecurity. The canonical scoring uses WFP standard weights (1, 2, 1, 1, 3).</t>
+          <t>Whether the woman consumed dairy products at meal-contributing quantities in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Le score de l'indice réduit des stratégies d'adaptation (rCSI) pour cette passation, calculé comme la somme pondérée des jours de fréquence de cinq stratégies d'adaptation. Plage 0-56. Des scores plus élevés indiquent une insécurité alimentaire plus grande. La notation canonique utilise les poids standard du PAM (1, 2, 1, 1, 3).</t>
+          <t>Si la femme a consommé des produits laitiers en quantités contribuant à un repas au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>El puntaje del Índice Reducido de Estrategias de Afrontamiento (rCSI) para esta aplicación, calculado como la suma ponderada de los días de frecuencia de cinco estrategias de afrontamiento. Rango 0-56. Puntajes más altos indican mayor inseguridad alimentaria. La puntuación canónica usa los pesos estándar del PMA (1, 2, 1, 1, 3).</t>
+          <t>Si la mujer consumió productos lácteos en cantidades que contribuyen a una comida en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr"/>
@@ -4210,22 +4114,26 @@
           <t>food_security</t>
         </is>
       </c>
-      <c r="K67" s="10" t="n"/>
+      <c r="K67" s="10" t="inlineStr">
+        <is>
+          <t>adolescent, adult</t>
+        </is>
+      </c>
       <c r="L67" s="10" t="inlineStr">
         <is>
-          <t>wfp_rcsi</t>
+          <t>fao_wdds</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>hdds_score</t>
+          <t>wdds_meat_poultry_fish_consumed</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -4235,17 +4143,17 @@
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>The Household Dietary Diversity Score for this administration, calculated as the simple count of food groups consumed during the recall period. Range 0-12. Categorical interpretation (bands) is program-specific and not standardized by FAO or FANTA; programs that apply thresholds should record the result via ScoringEvent.</t>
+          <t>Whether the woman consumed an item from the meat, poultry, and fish food group in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Le score de diversité alimentaire des ménages (HDDS) pour cette passation, calculé comme le décompte simple des groupes alimentaires consommés pendant la période de rappel. Plage 0-12. L'interprétation catégorielle (bandes) est spécifique au programme et non standardisée par la FAO ou FANTA ; les programmes appliquant des seuils doivent enregistrer le résultat via ScoringEvent.</t>
+          <t>Si la femme a consommé un aliment du groupe de la viande, de la volaille et du poisson au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>El puntaje de diversidad dietética del hogar (HDDS) para esta aplicación, calculado como el conteo simple de grupos alimentarios consumidos durante el período de recordatorio. Rango 0-12. La interpretación categórica (bandas) es específica del programa y no está estandarizada por la FAO ni FANTA; los programas que apliquen umbrales deben registrar el resultado mediante ScoringEvent.</t>
+          <t>Si la mujer consumió un alimento del grupo de carne, aves y pescado en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr"/>
@@ -4260,22 +4168,26 @@
           <t>food_security</t>
         </is>
       </c>
-      <c r="K68" s="8" t="n"/>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
+          <t>adolescent, adult</t>
+        </is>
+      </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
-          <t>fao_hdds</t>
+          <t>fao_wdds</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>mdd_w_score</t>
+          <t>wdds_eggs_consumed</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -4285,17 +4197,17 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>The Minimum Dietary Diversity for Women score for this administration, calculated as the count of food groups consumed out of the 10 MDD-W food groups during the recall period. Range 0-10.</t>
+          <t>Whether the woman consumed eggs in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Le score de diversité alimentaire minimum des femmes (MDD-W) pour cette passation, calculé comme le décompte des groupes alimentaires consommés parmi les 10 groupes alimentaires MDD-W pendant la période de rappel. Plage 0-10.</t>
+          <t>Si la femme a consommé des œufs au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>El puntaje de diversidad dietética mínima para mujeres (MDD-W) para esta aplicación, calculado como el conteo de grupos alimentarios consumidos de los 10 grupos alimentarios MDD-W durante el período de recordatorio. Rango 0-10.</t>
+          <t>Si la mujer consumió huevos en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr"/>
@@ -4310,17 +4222,21 @@
           <t>food_security</t>
         </is>
       </c>
-      <c r="K69" s="10" t="n"/>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>adolescent, adult</t>
+        </is>
+      </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>fao_mdd_w</t>
+          <t>fao_wdds</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>mdd_w_achieved</t>
+          <t>wdds_dark_green_leafy_veg_consumed</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
@@ -4335,17 +4251,17 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>True when mdd_w_score is 5 or more of the 10 MDD-W food groups, indicating that the woman met the minimum dietary diversity threshold. This is the FAO/FHI 360 standard binary indicator from the MDD-W guidelines (2016).</t>
+          <t>Whether the woman consumed dark green leafy vegetables in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Vrai lorsque le mdd_w_score est de 5 ou plus des 10 groupes alimentaires MDD-W, indiquant que la femme a atteint le seuil de diversité alimentaire minimum. Il s'agit de l'indicateur binaire standard FAO/FHI 360 des directives MDD-W (2016).</t>
+          <t>Si la femme a consommé des légumes-feuilles vert foncé au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>Verdadero cuando el mdd_w_score es 5 o más de los 10 grupos alimentarios MDD-W, indicando que la mujer alcanzó el umbral de diversidad dietética mínima. Es el indicador binario estándar FAO/FHI 360 de las directrices MDD-W (2016).</t>
+          <t>Si la mujer consumió hortalizas de hoja verde oscuro en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr"/>
@@ -4360,22 +4276,26 @@
           <t>food_security</t>
         </is>
       </c>
-      <c r="K70" s="8" t="n"/>
+      <c r="K70" s="8" t="inlineStr">
+        <is>
+          <t>adolescent, adult</t>
+        </is>
+      </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
-          <t>fao_mdd_w</t>
+          <t>fao_wdds</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>hhs_score</t>
+          <t>wdds_vitamin_a_fruit_veg_consumed</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -4385,17 +4305,17 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>The Household Hunger Scale score for this administration, calculated by recoding the three HHS frequency questions and summing. Recoding per FANTA HHS Indicator Guide: never = 0, rarely (1-2 times) = 1, sometimes (3-10 times) or often (&gt; 10 times) = 2. Range 0-6. Higher scores indicate greater household hunger.</t>
+          <t>Whether the woman consumed other vitamin-A-rich fruits and vegetables (orange-fleshed sweet potato, mango, papaya, carrot, pumpkin) in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Le score de l'échelle de la faim des ménages (HHS) pour cette passation, calculé en recodant les trois questions de fréquence HHS et en sommant. Recodage selon le Guide des indicateurs HHS de FANTA : jamais = 0, rarement (1-2 fois) = 1, parfois (3-10 fois) ou souvent (&gt; 10 fois) = 2. Plage 0-6. Des scores plus élevés indiquent une faim plus importante du ménage.</t>
+          <t>Si la femme a consommé d'autres fruits et légumes riches en vitamine A (patate douce à chair orange, mangue, papaye, carotte, citrouille) au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>El puntaje de la Escala de Hambre del Hogar (HHS) para esta aplicación, calculado recodificando las tres preguntas de frecuencia HHS y sumando. Recodificación según la Guía de indicadores HHS de FANTA: nunca = 0, raramente (1-2 veces) = 1, a veces (3-10 veces) o frecuentemente (&gt; 10 veces) = 2. Rango 0-6. Puntajes más altos indican mayor hambre del hogar.</t>
+          <t>Si la mujer consumió otras frutas y verduras ricas en vitamina A (batata de pulpa naranja, mango, papaya, zanahoria, calabaza) en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr"/>
@@ -4410,22 +4330,26 @@
           <t>food_security</t>
         </is>
       </c>
-      <c r="K71" s="10" t="n"/>
+      <c r="K71" s="10" t="inlineStr">
+        <is>
+          <t>adolescent, adult</t>
+        </is>
+      </c>
       <c r="L71" s="10" t="inlineStr">
         <is>
-          <t>fanta_hhs</t>
+          <t>fao_wdds</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>hhs_category</t>
+          <t>wdds_other_vegetables_consumed</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -4435,24 +4359,20 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>The household hunger category derived from hhs_score using FANTA standard thresholds: little to none (0-1), moderate (2-3), severe (4-5), very severe (6). Four categories per the FANTA HHS Indicator Guide (2010, revised 2017).</t>
+          <t>Whether the woman consumed other vegetables (not dark green leafy or vitamin-A-rich) in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>La catégorie de faim du ménage dérivée du hhs_score selon les seuils standard de FANTA : peu ou pas (0-1), modérée (2-3), sévère (4-5), très sévère (6). Quatre catégories selon le Guide des indicateurs HHS de FANTA (2010, révisé 2017).</t>
+          <t>Si la femme a consommé d'autres légumes (ni légumes-feuilles vert foncé ni riches en vitamine A) au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>La categoría de hambre del hogar derivada del hhs_score según los umbrales estándar de FANTA: poca o ninguna (0-1), moderada (2-3), grave (4-5), muy grave (6). Cuatro categorías según la Guía de indicadores HHS de FANTA (2010, revisada 2017).</t>
-        </is>
-      </c>
-      <c r="G72" s="8" t="inlineStr">
-        <is>
-          <t>hhs-category</t>
-        </is>
-      </c>
+          <t>Si la mujer consumió otras verduras (que no sean de hoja verde oscuro ni ricas en vitamina A) en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr"/>
       <c r="H72" s="8" t="inlineStr">
         <is>
           <t>draft</t>
@@ -4464,22 +4384,26 @@
           <t>food_security</t>
         </is>
       </c>
-      <c r="K72" s="8" t="n"/>
+      <c r="K72" s="8" t="inlineStr">
+        <is>
+          <t>adolescent, adult</t>
+        </is>
+      </c>
       <c r="L72" s="8" t="inlineStr">
         <is>
-          <t>fanta_hhs</t>
+          <t>fao_wdds</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>fies_raw_score</t>
+          <t>wdds_other_fruits_consumed</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -4489,17 +4413,17 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>The raw Food Insecurity Experience Scale score for this administration, calculated as the count of affirmative responses to the eight FIES items. Range 0-8. The Rasch-model-adjusted FIES scale score used for population-level prevalence estimation (SDG 2.1.2) requires calibration data and is not a per-record field; it belongs on a ScoringEvent.</t>
+          <t>Whether the woman consumed other fruits (not vitamin-A-rich) in the past 24 hours. One of ten food groups in the FAO Minimum Dietary Diversity for Women (MDD-W) indicator.</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Le score brut de l'échelle d'expérience de l'insécurité alimentaire (FIES) pour cette passation, calculé comme le décompte des réponses affirmatives aux huit items FIES. Plage 0-8. Le score ajusté par modèle de Rasch utilisé pour l'estimation de la prévalence au niveau de la population (ODD 2.1.2) nécessite des données de calibrage et n'est pas un champ par enregistrement ; il relève d'un ScoringEvent.</t>
+          <t>Si la femme a consommé d'autres fruits (non riches en vitamine A) au cours des dernières 24 heures. L'un des dix groupes alimentaires de l'indicateur de Diversité alimentaire minimale pour les femmes (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>El puntaje bruto de la Escala de Experiencia de Inseguridad Alimentaria (FIES) para esta aplicación, calculado como el conteo de respuestas afirmativas a los ocho ítems FIES. Rango 0-8. El puntaje ajustado por modelo Rasch usado para la estimación de prevalencia poblacional (ODS 2.1.2) requiere datos de calibración y no es un campo por registro; corresponde a un ScoringEvent.</t>
+          <t>Si la mujer consumió otras frutas (que no sean ricas en vitamina A) en las últimas 24 horas. Uno de los diez grupos alimentarios del indicador de Diversidad Dietética Mínima para Mujeres (MDD-W) de la FAO.</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr"/>
@@ -4514,22 +4438,26 @@
           <t>food_security</t>
         </is>
       </c>
-      <c r="K73" s="10" t="n"/>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>adolescent, adult</t>
+        </is>
+      </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>fao_fies</t>
+          <t>fao_wdds</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>lcs_band</t>
+          <t>recall_period_days</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -4539,24 +4467,20 @@
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>The livelihood coping severity band for this administration, derived by classifying the household into the highest severity tier of any strategy it adopted. Strategies are grouped into three tiers (stress, crisis, emergency) per the WFP CARI Guidelines. A strategy is considered adopted if the response is 'yes' or 'already exhausted'. If no strategy was adopted, the band is 'none'. This is the canonical worst-case classification used in WFP food security analysis.</t>
+          <t>Number of days of recall for instrument items that allow a variable reference period, primarily FIES (commonly 30 or 365 days) and HDDS/WDDS variants. May be omitted when the reference period is fixed by the instrument protocol, but populating it explicitly is valid and can aid data quality verification. Canonical recall periods by instrument: FCS 7 days, rCSI 7 days, HDDS 1 day, MDD-W 1 day, FIES 30 days (operational monitoring) or 365 days (SDG 2.1.2), HHS 30 days, LCS 30 days, MAHFP 12 months. Multi-instrument profiles pick one value, typically the longest.</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>Le niveau de sévérité des stratégies de moyens d'existence pour cette passation, dérivé en classant le ménage au niveau de sévérité le plus élevé de toute stratégie adoptée. Les stratégies sont regroupées en trois niveaux (stress, crise, urgence) selon les directives CARI du PAM. Une stratégie est considérée comme adoptée si la réponse est « oui » ou « déjà épuisée ». Si aucune stratégie n'a été adoptée, le niveau est « aucune ». Il s'agit de la classification canonique du pire cas utilisée dans l'analyse de sécurité alimentaire du PAM.</t>
+          <t>Nombre de jours de rappel pour les items d'instruments permettant une période de référence variable, principalement FIES (couramment 30 ou 365 jours) et les variantes HDDS/MDD-W. Peut être omis lorsque la période de référence est fixée par le protocole de l'instrument, mais le renseigner explicitement est valide et peut faciliter la vérification de la qualité des données. Périodes de rappel canoniques par instrument : FCS 7 jours, rCSI 7 jours, HDDS 1 jour, MDD-W 1 jour, FIES 30 jours (suivi opérationnel) ou 365 jours (ODD 2.1.2), HHS 30 jours, LCS 30 jours, MAHFP 12 mois. Les profils multi-instruments choisissent une valeur, généralement la plus longue.</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>El nivel de severidad de las estrategias de medios de vida para esta aplicación, derivado clasificando al hogar en el nivel de severidad más alto de cualquier estrategia adoptada. Las estrategias se agrupan en tres niveles (estrés, crisis, emergencia) según las directrices CARI del PMA. Una estrategia se considera adoptada si la respuesta es «sí» o «ya agotada». Si no se adoptó ninguna estrategia, el nivel es «ninguna». Es la clasificación canónica del peor caso utilizada en el análisis de seguridad alimentaria del PMA.</t>
-        </is>
-      </c>
-      <c r="G74" s="8" t="inlineStr">
-        <is>
-          <t>lcs-band</t>
-        </is>
-      </c>
+          <t>Número de días de recordatorio para los ítems de instrumentos que permiten un período de referencia variable, principalmente FIES (comúnmente 30 o 365 días) y variantes HDDS/MDD-W. Puede omitirse cuando el período de referencia está fijado por el protocolo del instrumento, pero registrarlo explícitamente es válido y puede facilitar la verificación de calidad de datos. Períodos de recordatorio canónicos por instrumento: FCS 7 días, rCSI 7 días, HDDS 1 día, MDD-W 1 día, FIES 30 días (monitoreo operativo) o 365 días (ODS 2.1.2), HHS 30 días, LCS 30 días, MAHFP 12 meses. Los perfiles multi-instrumento eligen un valor, generalmente el más largo.</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr"/>
       <c r="H74" s="8" t="inlineStr">
         <is>
           <t>draft</t>
@@ -4565,11 +4489,519 @@
       <c r="I74" s="8" t="n"/>
       <c r="J74" s="8" t="inlineStr">
         <is>
-          <t>food_security</t>
+          <t>context</t>
         </is>
       </c>
       <c r="K74" s="8" t="n"/>
-      <c r="L74" s="8" t="inlineStr">
+      <c r="L74" s="8" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>fcs_score</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>The weighted Food Consumption Score for this administration, calculated as the sum of food-group frequency days multiplied by their WFP standard weights. Range 0-112. The canonical scoring uses nine food groups with weights from the WFP FCS Technical Guidance Note (2015).</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>Le score de consommation alimentaire (FCS) pondéré pour cette passation, calculé comme la somme des jours de fréquence par groupe alimentaire multipliés par leurs poids standard du PAM. Plage 0-112. La notation canonique utilise neuf groupes alimentaires avec les poids du Guide technique FCS du PAM (2015).</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>El puntaje ponderado de consumo alimentario (FCS) para esta aplicación, calculado como la suma de los días de frecuencia por grupo alimentario multiplicados por sus pesos estándar del PMA. Rango 0-112. La puntuación canónica usa nueve grupos alimentarios con los pesos de la Guía Técnica FCS del PMA (2015).</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr"/>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="n"/>
+      <c r="J75" s="10" t="inlineStr">
+        <is>
+          <t>food_security</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="n"/>
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>wfp_fcs</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>fcs_consumption_group</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>The food consumption group derived from fcs_score using WFP-published thresholds. Both the standard set (21/35) and the high-sugar/high-oil set (28/42) are WFP-canonical and valid for this field. Use ScoringEvent only for thresholds not published by WFP (national adaptations, researcher-defined cutoffs). Standard thresholds: poor (0-21), borderline (21.5-35), acceptable (&gt; 35). Adjusted thresholds for high-sugar/high-oil contexts: poor (0-28), borderline (28.5-42), acceptable (&gt; 42).</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>Le groupe de consommation alimentaire dérivé du fcs_score selon les seuils publiés par le PAM. Les seuils standard (21/35) et les seuils ajustés pour les régimes riches en sucre ou en huile (28/42) sont tous deux canoniques et valides pour ce champ. Utiliser ScoringEvent uniquement pour des seuils non publiés par le PAM (adaptations nationales, seuils définis par des chercheurs). Seuils standard : pauvre (0-21), limite (21,5-35), acceptable (&gt; 35). Seuils ajustés : pauvre (0-28), limite (28,5-42), acceptable (&gt; 42).</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>El grupo de consumo alimentario derivado del fcs_score según los umbrales publicados por el PMA. Tanto el conjunto estándar (21/35) como el conjunto ajustado para dietas altas en azúcar o aceite (28/42) son canónicos del PMA y válidos para este campo. Usar ScoringEvent solo para umbrales no publicados por el PMA (adaptaciones nacionales, cortes definidos por investigadores). Umbrales estándar: pobre (0-21), límite (21,5-35), aceptable (&gt; 35). Umbrales ajustados: pobre (0-28), límite (28,5-42), aceptable (&gt; 42).</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>food-consumption-group</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I76" s="8" t="n"/>
+      <c r="J76" s="8" t="inlineStr">
+        <is>
+          <t>food_security</t>
+        </is>
+      </c>
+      <c r="K76" s="8" t="n"/>
+      <c r="L76" s="8" t="inlineStr">
+        <is>
+          <t>wfp_fcs</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>rcsi_score</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>The reduced Coping Strategies Index score for this administration, calculated as the weighted sum of five coping strategy frequency days. Range 0-56. Higher scores indicate greater food insecurity. The canonical scoring uses WFP standard weights (1, 2, 1, 1, 3).</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>Le score de l'indice réduit des stratégies d'adaptation (rCSI) pour cette passation, calculé comme la somme pondérée des jours de fréquence de cinq stratégies d'adaptation. Plage 0-56. Des scores plus élevés indiquent une insécurité alimentaire plus grande. La notation canonique utilise les poids standard du PAM (1, 2, 1, 1, 3).</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>El puntaje del Índice Reducido de Estrategias de Afrontamiento (rCSI) para esta aplicación, calculado como la suma ponderada de los días de frecuencia de cinco estrategias de afrontamiento. Rango 0-56. Puntajes más altos indican mayor inseguridad alimentaria. La puntuación canónica usa los pesos estándar del PMA (1, 2, 1, 1, 3).</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="inlineStr"/>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I77" s="10" t="n"/>
+      <c r="J77" s="10" t="inlineStr">
+        <is>
+          <t>food_security</t>
+        </is>
+      </c>
+      <c r="K77" s="10" t="n"/>
+      <c r="L77" s="10" t="inlineStr">
+        <is>
+          <t>wfp_rcsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>hdds_score</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>The Household Dietary Diversity Score for this administration, calculated as the simple count of food groups consumed during the recall period. Range 0-12. Categorical interpretation (bands) is program-specific and not standardized by FAO or FANTA; programs that apply thresholds should record the result via ScoringEvent.</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>Le score de diversité alimentaire des ménages (HDDS) pour cette passation, calculé comme le décompte simple des groupes alimentaires consommés pendant la période de rappel. Plage 0-12. L'interprétation catégorielle (bandes) est spécifique au programme et non standardisée par la FAO ou FANTA ; les programmes appliquant des seuils doivent enregistrer le résultat via ScoringEvent.</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>El puntaje de diversidad dietética del hogar (HDDS) para esta aplicación, calculado como el conteo simple de grupos alimentarios consumidos durante el período de recordatorio. Rango 0-12. La interpretación categórica (bandas) es específica del programa y no está estandarizada por la FAO ni FANTA; los programas que apliquen umbrales deben registrar el resultado mediante ScoringEvent.</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr"/>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I78" s="8" t="n"/>
+      <c r="J78" s="8" t="inlineStr">
+        <is>
+          <t>food_security</t>
+        </is>
+      </c>
+      <c r="K78" s="8" t="n"/>
+      <c r="L78" s="8" t="inlineStr">
+        <is>
+          <t>fao_hdds</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>mdd_w_score</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>The Minimum Dietary Diversity for Women score for this administration, calculated as the count of food groups consumed out of the 10 MDD-W food groups during the recall period. Range 0-10.</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>Le score de diversité alimentaire minimum des femmes (MDD-W) pour cette passation, calculé comme le décompte des groupes alimentaires consommés parmi les 10 groupes alimentaires MDD-W pendant la période de rappel. Plage 0-10.</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>El puntaje de diversidad dietética mínima para mujeres (MDD-W) para esta aplicación, calculado como el conteo de grupos alimentarios consumidos de los 10 grupos alimentarios MDD-W durante el período de recordatorio. Rango 0-10.</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr"/>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="n"/>
+      <c r="J79" s="10" t="inlineStr">
+        <is>
+          <t>food_security</t>
+        </is>
+      </c>
+      <c r="K79" s="10" t="n"/>
+      <c r="L79" s="10" t="inlineStr">
+        <is>
+          <t>fao_mdd_w</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>mdd_w_achieved</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>True when mdd_w_score is 5 or more of the 10 MDD-W food groups, indicating that the woman met the minimum dietary diversity threshold. This is the FAO/FHI 360 standard binary indicator from the MDD-W guidelines (2016).</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>Vrai lorsque le mdd_w_score est de 5 ou plus des 10 groupes alimentaires MDD-W, indiquant que la femme a atteint le seuil de diversité alimentaire minimum. Il s'agit de l'indicateur binaire standard FAO/FHI 360 des directives MDD-W (2016).</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>Verdadero cuando el mdd_w_score es 5 o más de los 10 grupos alimentarios MDD-W, indicando que la mujer alcanzó el umbral de diversidad dietética mínima. Es el indicador binario estándar FAO/FHI 360 de las directrices MDD-W (2016).</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I80" s="8" t="n"/>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>food_security</t>
+        </is>
+      </c>
+      <c r="K80" s="8" t="n"/>
+      <c r="L80" s="8" t="inlineStr">
+        <is>
+          <t>fao_mdd_w</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>hhs_score</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>The Household Hunger Scale score for this administration, calculated by recoding the three HHS frequency questions and summing. Recoding per FANTA HHS Indicator Guide: never = 0, rarely (1-2 times) = 1, sometimes (3-10 times) or often (&gt; 10 times) = 2. Range 0-6. Higher scores indicate greater household hunger.</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>Le score de l'échelle de la faim des ménages (HHS) pour cette passation, calculé en recodant les trois questions de fréquence HHS et en sommant. Recodage selon le Guide des indicateurs HHS de FANTA : jamais = 0, rarement (1-2 fois) = 1, parfois (3-10 fois) ou souvent (&gt; 10 fois) = 2. Plage 0-6. Des scores plus élevés indiquent une faim plus importante du ménage.</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>El puntaje de la Escala de Hambre del Hogar (HHS) para esta aplicación, calculado recodificando las tres preguntas de frecuencia HHS y sumando. Recodificación según la Guía de indicadores HHS de FANTA: nunca = 0, raramente (1-2 veces) = 1, a veces (3-10 veces) o frecuentemente (&gt; 10 veces) = 2. Rango 0-6. Puntajes más altos indican mayor hambre del hogar.</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr"/>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>food_security</t>
+        </is>
+      </c>
+      <c r="K81" s="10" t="n"/>
+      <c r="L81" s="10" t="inlineStr">
+        <is>
+          <t>fanta_hhs</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>hhs_category</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>The household hunger category derived from hhs_score using FANTA standard thresholds: little to none (0-1), moderate (2-3), severe (4-5), very severe (6). Four categories per the FANTA HHS Indicator Guide (2010, revised 2017).</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>La catégorie de faim du ménage dérivée du hhs_score selon les seuils standard de FANTA : peu ou pas (0-1), modérée (2-3), sévère (4-5), très sévère (6). Quatre catégories selon le Guide des indicateurs HHS de FANTA (2010, révisé 2017).</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>La categoría de hambre del hogar derivada del hhs_score según los umbrales estándar de FANTA: poca o ninguna (0-1), moderada (2-3), grave (4-5), muy grave (6). Cuatro categorías según la Guía de indicadores HHS de FANTA (2010, revisada 2017).</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>hhs-category</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="n"/>
+      <c r="J82" s="8" t="inlineStr">
+        <is>
+          <t>food_security</t>
+        </is>
+      </c>
+      <c r="K82" s="8" t="n"/>
+      <c r="L82" s="8" t="inlineStr">
+        <is>
+          <t>fanta_hhs</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>fies_raw_score</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>The raw Food Insecurity Experience Scale score for this administration, calculated as the count of affirmative responses to the eight FIES items. Range 0-8. The Rasch-model-adjusted FIES scale score used for population-level prevalence estimation (SDG 2.1.2) requires calibration data and is not a per-record field; it belongs on a ScoringEvent.</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>Le score brut de l'échelle d'expérience de l'insécurité alimentaire (FIES) pour cette passation, calculé comme le décompte des réponses affirmatives aux huit items FIES. Plage 0-8. Le score ajusté par modèle de Rasch utilisé pour l'estimation de la prévalence au niveau de la population (ODD 2.1.2) nécessite des données de calibrage et n'est pas un champ par enregistrement ; il relève d'un ScoringEvent.</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>El puntaje bruto de la Escala de Experiencia de Inseguridad Alimentaria (FIES) para esta aplicación, calculado como el conteo de respuestas afirmativas a los ocho ítems FIES. Rango 0-8. El puntaje ajustado por modelo Rasch usado para la estimación de prevalencia poblacional (ODS 2.1.2) requiere datos de calibración y no es un campo por registro; corresponde a un ScoringEvent.</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr"/>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="n"/>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>food_security</t>
+        </is>
+      </c>
+      <c r="K83" s="10" t="n"/>
+      <c r="L83" s="10" t="inlineStr">
+        <is>
+          <t>fao_fies</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>lcs_band</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>The livelihood coping severity band for this administration, derived by classifying the household into the highest severity tier of any strategy it adopted. Strategies are grouped into three tiers (stress, crisis, emergency) per the WFP CARI Guidelines. A strategy is considered adopted if the response is 'yes' or 'already exhausted'. If no strategy was adopted, the band is 'none'. This is the canonical worst-case classification used in WFP food security analysis.</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>Le niveau de sévérité des stratégies de moyens d'existence pour cette passation, dérivé en classant le ménage au niveau de sévérité le plus élevé de toute stratégie adoptée. Les stratégies sont regroupées en trois niveaux (stress, crise, urgence) selon les directives CARI du PAM. Une stratégie est considérée comme adoptée si la réponse est « oui » ou « déjà épuisée ». Si aucune stratégie n'a été adoptée, le niveau est « aucune ». Il s'agit de la classification canonique du pire cas utilisée dans l'analyse de sécurité alimentaire du PAM.</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>El nivel de severidad de las estrategias de medios de vida para esta aplicación, derivado clasificando al hogar en el nivel de severidad más alto de cualquier estrategia adoptada. Las estrategias se agrupan en tres niveles (estrés, crisis, emergencia) según las directrices CARI del PMA. Una estrategia se considera adoptada si la respuesta es «sí» o «ya agotada». Si no se adoptó ninguna estrategia, el nivel es «ninguna». Es la clasificación canónica del peor caso utilizada en el análisis de seguridad alimentaria del PMA.</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>lcs-band</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="n"/>
+      <c r="J84" s="8" t="inlineStr">
+        <is>
+          <t>food_security</t>
+        </is>
+      </c>
+      <c r="K84" s="8" t="n"/>
+      <c r="L84" s="8" t="inlineStr">
         <is>
           <t>wfp_lcs, wfp_cari</t>
         </is>

--- a/site/public/FoodSecurityProfile-definition.xlsx
+++ b/site/public/FoodSecurityProfile-definition.xlsx
@@ -9,11 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concept" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Properties" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lcs-frequency" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hhs-frequency" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="food-consumption-group" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hhs-category" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lcs-band" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="administration-mode" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="relationship-type" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lcs-frequency" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hhs-frequency" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="food-consumption-group" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hhs-category" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lcs-band" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5021,6 +5023,615 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Label (EN)</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Label (FR)</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Label (ES)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Definition (EN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Self-report</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Auto-déclaration</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Autoinforme</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>The subject answered the items about themselves. Preferred mode for WG-SS and WG-ES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Proxy-report</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Déclaration par procuration</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Informe por terceros</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Another person (caregiver, parent, spouse, household member) answered the items about the subject. Always the mode for the UNICEF Child Functioning Module, because the child is not the respondent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>assisted</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Assisted</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Assisté</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Asistido</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>The subject answered the items but received help from another person (for reading, translation, or comprehension). Distinct from proxy: the subject is still the respondent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Mixte</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Some items were answered by the subject and others by a proxy. Use when the administration crossed modes within one session, for example because the subject tired or could not answer certain items.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Label (EN)</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Label (FR)</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Label (ES)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Definition (EN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>spouse</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Conjoint(e)</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Cónyuge</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>A person's husband, wife, or legally recognized partner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Padre/Madre</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>A biological or legally recognized mother or father.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Enfant</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Hijo/a</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>A biological or legally recognized son or daughter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>sibling</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Sibling</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Frère/Sœur</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Hermano/a</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>A brother or sister sharing at least one biological or legal parent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>grandparent</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Grandparent</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Grand-parent</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Abuelo/a</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>A parent of a person's parent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>grandchild</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Grandchild</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Petit-enfant</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Nieto/a</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>A child of a person's child.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Guardian</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Tuteur/Tutrice</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Tutor/a</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>A person with legal responsibility for the care and management of another, typically a minor or incapacitated adult.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>caregiver</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Caregiver</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Soignant(e)</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Cuidador/a</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>A person who provides ongoing care or assistance, whether or not they hold legal guardianship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>dependent</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Personne à charge</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Dependiente</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>A person who relies on another for financial support or daily living needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>in_law</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>In-law</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Par alliance</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Pariente político</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>A person related through marriage rather than by blood, such as a parent-in-law, child-in-law, or sibling-in-law.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>extended_family</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Extended family</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Famille élargie</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Familia extendida</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>A family member beyond the immediate kinship categories (e.g. aunt, uncle, cousin, niece, nephew) where the specific type is not recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>payment_proxy</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Payment proxy</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Mandataire de paiement</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Apoderado de pago</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>A person authorized to collect benefits on behalf of another, often used when the beneficiary cannot collect in person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>survivor</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Survivor</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Survivant(e)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Sobreviviente</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>A person entitled to continued or transferred benefits following the death of the primary beneficiary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>non_relative</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Non-relative</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Non-parent</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>No pariente</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>A person known to the household or group who has no kinship or legal tie to the reference person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Autre</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>A relationship type not covered by the other categories.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
@@ -5168,7 +5779,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5324,7 +5935,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5453,7 +6064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5609,7 +6220,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
